--- a/data/source/2026-09-28/BSR_DE_Wet-Dry-Floor-Washer_Top50_2026-09-28.xlsx
+++ b/data/source/2026-09-28/BSR_DE_Wet-Dry-Floor-Washer_Top50_2026-09-28.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="739" uniqueCount="147">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="806" uniqueCount="360">
   <si>
     <t>#</t>
   </si>
@@ -232,184 +232,882 @@
     <t>B0GJSLTZK3</t>
   </si>
   <si>
-    <t>https://www.amazon.deundefined</t>
-  </si>
-  <si>
-    <t>roborock F25 GT Gen 2 Set Nass-Trockensauger, 20.000 Pa, 180° Lay-FlatsAkkusauger mit Wischfunktion, 90 °C Hochtemperatur-S</t>
+    <t>Größe: F25 GT Gen 2 Set</t>
+  </si>
+  <si>
+    <t>Marke: roborock | Besonderes Merkmal: Kabellos | Filtertyp: Waschbarer Filter | Oberflächenempfehlung: Harter Boden | Stromquelle: Kabellos</t>
+  </si>
+  <si>
+    <t>roborock</t>
+  </si>
+  <si>
+    <t>https://www.amazon.denull</t>
+  </si>
+  <si>
+    <t>roborock F25 GT Gen 2 Set Nass-Trockensauger, 20.000 Pa, 180° Lay-Flat</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.000 Pa Intelligente Nass- und Trockenreinigung : Liefert starke Saugkraft, die mit Kaffee, Ketchup, Tierfutter und Haaren fertig wird. Mit einem Abwärtsdruck von 20 N und 450 Reinigungsbewegungen pro Minute reinigt er Marmor-, Holz-, Fliesen- und Laminatböden gründlich und effektiv.
+180° FlatReach 2.0 und Dreifach-Kantenreinigung : Das 12,5 cm ultraflache Design reicht unter Möbel, die volle Saugleistung von 20.000 Pa bleibt erhalten. Umfassende Kantenreinigung in jeder Ecke, an Fußleisten und an Stufen sorgt überall für eine gründliche Reinigung.
+Verhedderungsfreies Design und geschmeidige Laufräder : Das JawScrapers verhedderungsfreie Design verhindert das Verwickeln von Haaren und ermöglicht kontinuierliche Leistung. Optimierte Laufräder und 70°-Schwenkwinkel gleiten mühelos über Schwelle; geringes Gewicht von nur 4 kg erleichtert das Schieben.
+90 °C Hochtemperatur-Selbstreinigung und Heißlufttrocknen : 360°-Rolle reinigt gründlich und verhindert Ablagerungen. 90 °C heiße Luft trocknet die Rolle in 30 Minuten und minimiert Feuchtigkeit. Ultra-leiser Betrieb mit 48,59 dB(A) eignet sich zur Reinigung in der Nacht.
+Lange Akkulaufzeit und integrierte intelligente Funktionen : Bis zu 38 Minuten ECO-Laufzeit reichen bis zu 284 m² ohne Unterbrechungen. Der Pausenmodus beim aufrechten Stehen lässt das Gerät eingeschaltet, ohne neu zu starten. Farbige LEDs und Sprachausgaben sorgen für einfach zugängliche Bedienung und Komfort.</t>
   </si>
   <si>
     <t>https://www.amazon.de/dp/B0GJSLTZK3?psc=1</t>
   </si>
   <si>
-    <t>https://images-eu.ssl-images-amazon.com/images/I/61AVz1Oy8NL._AC_UL300_SR300,200_.jpg</t>
+    <t>https://images-na.ssl-images-amazon.com/images/I/61AVz1Oy8NL._AC_US600_.jpg</t>
+  </si>
+  <si>
+    <t>B0H8LGC3LM</t>
+  </si>
+  <si>
+    <t>Küche, Haushalt &amp; Wohnen:Haushaltsreiniger &amp; Staubsauger:Staubsauger:Nass-/Trockensauger für den Haushalt</t>
+  </si>
+  <si>
+    <t>Küche, Haushalt &amp; Wohnen</t>
+  </si>
+  <si>
+    <t>Nass-/Trockensauger für den Haushalt</t>
+  </si>
+  <si>
+    <t>1</t>
+  </si>
+  <si>
+    <t>1,000</t>
+  </si>
+  <si>
+    <t>2026-04-20</t>
+  </si>
+  <si>
+    <t>NA</t>
+  </si>
+  <si>
+    <t>Amazon</t>
+  </si>
+  <si>
+    <t>Y</t>
+  </si>
+  <si>
+    <t>Amazons Tipp</t>
+  </si>
+  <si>
+    <t>9 Pfund</t>
+  </si>
+  <si>
+    <t>30.5 x 30.5 x 114.3 cm</t>
+  </si>
+  <si>
+    <t>30.50 x 30.50 x 114.30 cm</t>
+  </si>
+  <si>
+    <t>8.09 kg</t>
+  </si>
+  <si>
+    <t>74.6 x 34.4 x 28.4 cm</t>
+  </si>
+  <si>
+    <t>74.60 x 34.40 x 28.40 cm</t>
+  </si>
+  <si>
+    <t>轻型标准大件</t>
   </si>
   <si>
     <t>B0FJGW9H14</t>
   </si>
   <si>
-    <t>Rowenta X-Clean 5, 2-in-1 Nass- und Trockensauger, 3 Modi, präzise Reinigung, automatischer Erkennungsmodus, LED-Beleuchtung,</t>
+    <t>Farbe: Weiß/Schwarz</t>
+  </si>
+  <si>
+    <t>Marke: Rowenta | Besonderes Merkmal: 2-in-1 saugen und wischen, 440 ml Schmutzwassertank, 730 ml Frischwassertank, LED Beleuchtung, Selbsteinigungs- und Trocknungssystem, automatische Schmutzerkennung, selbstfahrendes System | Filtertyp: Schaum | Oberflächenempfehlung: Fugenmörtel, Fliese, Boden, Arbeitsfläche | Stromquelle: Batteriebetrieben</t>
+  </si>
+  <si>
+    <t>Rowenta</t>
+  </si>
+  <si>
+    <t>https://www.amazon.de/stores/Rowenta/page/F8BD1336-17F4-4FC9-B31C-02321E3AC422?lp_asin=B0FJGW9H14&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto</t>
+  </si>
+  <si>
+    <t>Rowenta X-Clean 5, 2-in-1 Nass- und Trockensauger, 3 Modi, präzise Reinigung, automatischer Erkennungsmodus, LED-Beleuchtung, selbstreinigend, Heißtrocknung, 50 Min. Laufzeit, Schneeweiß, GZ5557EE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Saugen und Wischen in einem Schritt: Entfernen Sie Staub und Schmutz in nur einem Durchgang – für streifenfreie Sauberkeit auf allen Hartböden und gründliche 2-Kantenreinigung
+Leichte Bedienung: Der integrierte Eigenantrieb macht das Wischen besonders leicht – mit nur 1,1 kg Gewicht in der Hand (Gesamtgewicht des Geräts 4,63kg); Wählen Sie per Knopfdruck zwischen Eco-, Max- oder Auto-Modus
+Kabellos mit langer Laufzeit: Bis zu 50 Minuten Reinigungszeit im Eco-Modus – kabellos, flexibel und ohne Unterbrechung; optimal für große Flächen und den täglichen Einsatz
+Selbstreinigung auf Knopfdruck: Nach dem Putzen reinigt sich das Gerät in nur 90 Sekunden selbst und trocknet automatisch bei 60 Grad – für hygienisch saubere Bürsten und frischen Duft
+Alles im Blick: Digitalanzeige, Sprachsteuerung und Automatikmodus machen die Reinigung noch einfacher; Dank LED-Beleuchtung am Kopfteil sehen Sie auch versteckten Schmutz
+Große Wassertanks für lange Reinigung: 730 ml Frischwasser- und 440 ml Schmutzwassertank – für gründliche Reinigung ohne häufiges Nachfüllen; optimal für Hartböden, Fliesen oder Laminat
+Umfangreiches Zubehör inklusive: Enthält eine zusätzliche Reinigungsrolle, ein Filter-Set für bis zu 200 Anwendungen, Ladestation und Reinigungsbürste</t>
   </si>
   <si>
     <t>https://www.amazon.de/dp/B0FJGW9H14?psc=1</t>
   </si>
   <si>
-    <t>https://images-eu.ssl-images-amazon.com/images/I/61ACeClalUL._AC_UL300_SR300,200_.jpg</t>
+    <t>https://images-na.ssl-images-amazon.com/images/I/61ACeClalUL._AC_US600_.jpg</t>
+  </si>
+  <si>
+    <t>B0HJRYCGD6</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>2025-09-24</t>
+  </si>
+  <si>
+    <t>4,7 Kilogramm</t>
+  </si>
+  <si>
+    <t>4.70 kg</t>
+  </si>
+  <si>
+    <t>28 x 21 x 115 cm</t>
+  </si>
+  <si>
+    <t>28.00 x 21.00 x 115.00 cm</t>
+  </si>
+  <si>
+    <t>9.9 kg</t>
+  </si>
+  <si>
+    <t>9.90 kg</t>
+  </si>
+  <si>
+    <t>76 x 35 x 30 cm</t>
+  </si>
+  <si>
+    <t>76.00 x 35.00 x 30.00 cm</t>
   </si>
   <si>
     <t>B0DJ7MYQ7X</t>
   </si>
   <si>
-    <t>roborock F25 LT Nass Trockensauger, 60 Min Laufzeit, 20.000 Pa Staubsaugers180° Lay-Flat Saugwischer, 90°C 5 Min Hochtemper</t>
+    <t>Set name: F25 LT</t>
+  </si>
+  <si>
+    <t>Marke: roborock | Besonderes Merkmal: Kabellos, Nass/Trocken, Saugleistung 20 kPa | Filtertyp: HEPA Filter | Oberflächenempfehlung: Harter Boden | Stromquelle: Batteriebetrieben</t>
+  </si>
+  <si>
+    <t>https://www.amazon.de/stores/roborock/page/68FE67F4-6CEB-4B2C-AE25-2300177358D6?lp_asin=B0DJ7MYQ7X&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto</t>
+  </si>
+  <si>
+    <t>roborock F25 LT Nass Trockensauger, 60 Min Laufzeit, 20.000 Pa Staubsauger</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mühelose Selbstreinigung &amp; Schnelltrocknung: Erlebe den Luxus eines selbstreinigenden Staubsaugermopps in einem! Mit einer leistungsstarken 90℃ (194℉) Hochtemperatur werden hartnäckiges Fett und Schmutz mühelos entfernt, so dass deine Hartböden makellos bleiben. Wähle zwischen einem kurzen 5-Minuten-Trocknungsmodus für die schnelle Reinigung oder einer ruhigen 30-Minuten-Option, um unbekümmert barfuß laufen zu können und es sich frisch und sauber anfühlt
+Schlankes Design im hingelegten Zustand mit voller Leistung: Verwandle deine Reinigungsroutine mit einem 180-Grad-Lay-Flat-Design, das mühelos unter Möbel gelangt, ohne die Saugleistung zu beeinträchtigen. Mit einer Dicke von nur 12,5 cm (4,92 Zoll) passt dieser Staubsauger auch in flache Bereiche und macht es zu einem Kinderspiel, an schwer zugängliche Bereiche zu gelangen, in denen sich Tierhaare gerne verstecken.
+Leistungsstarke All-in-One-Reinigungslösung: Revolutioniere die Reinigung mit diesem Nass-Trockensauger, der die Effizienz von Besen, Staubsauger und Mopp in einem eleganten Paket vereint. Mit einer erstaunlichen Saugleistung von 20.000 Pa saugt er alles auf, von Schmutz bis hin zu Tierhaaren, und sorgt so dafür, dass selbst die geschäftigsten Haushalte mit minimalem Aufwand makellos sauber bleiben. Diese Staubsauger-Mopp-Kombination definiert Komfort wirklich neu
+Schlierenfrei &amp; kein Feststecken: Verabschiede dich von Strähnen und verheddertem Haar mit unserem innovativen Doppelschabersystem. Dieser Staubsauger ist so konzipiert, dass er mit Wasser umgehen kann, ohne zu verstopfen, und jedes Mal ein makelloses Ergebnis liefert. Mit Zertifikaten von SGS und TÜV im Rücken, können Sie beruhigt reinigen, denn Sie wissen, dass Ihre harten Böden ohne unansehnliche Rückstände glänzen werden.
+Reinigung bis an die Kanten &amp; müheloses Manövrieren: Mach dich bereit für eine Reinigung an Kanten mit einem Abstand von nur 1 mm (&lt;0,03 Zoll) zu Fußleisten, Treppen und Couches. Keine übersehenen Stellen oder lästigen Tierhaare mehr, die sich in Ecken verstecken! Der flexible 70°-Kopf und der strategisch positionierte Wassertank sorgen für ein optimales Gleichgewicht, so dass dieser Staubsauger sanft über alle Arten von Bodenbelägen gleitet und jede Reinigung zu einem angenehmen Erlebnis macht.</t>
   </si>
   <si>
     <t>https://www.amazon.de/dp/B0DJ7MYQ7X?psc=1</t>
   </si>
   <si>
-    <t>https://images-eu.ssl-images-amazon.com/images/I/51li4JItSNL._AC_UL300_SR300,200_.jpg</t>
+    <t>https://images-na.ssl-images-amazon.com/images/I/51li4JItSNL._AC_US600_.jpg</t>
+  </si>
+  <si>
+    <t>B0HKMTL7TP</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>2025-02-26</t>
+  </si>
+  <si>
+    <t>AMZ</t>
+  </si>
+  <si>
+    <t>4,2 Kilogramm</t>
+  </si>
+  <si>
+    <t>4.20 kg</t>
+  </si>
+  <si>
+    <t>26.2 x 22.1 x 110 cm</t>
+  </si>
+  <si>
+    <t>26.20 x 22.10 x 110.00 cm</t>
+  </si>
+  <si>
+    <t>8.28 kg</t>
+  </si>
+  <si>
+    <t>72.6 x 34.4 x 29.8 cm</t>
+  </si>
+  <si>
+    <t>72.60 x 34.40 x 29.80 cm</t>
   </si>
   <si>
     <t>B0DPP6C5YP</t>
   </si>
   <si>
-    <t>Tineco Floor ONE S9 Artist Smart Nass-Trockensauger, SmoothDrive, DualBlocks180° Lie Flat Waschsauger, 22000Pa Nasssauger,</t>
+    <t>Set name: S9 Artist</t>
+  </si>
+  <si>
+    <t>Marke: Tineco | Besonderes Merkmal: 22.000Pa Saugkraft, 360°-Antrieb in alle Richtungen, Automatsiche Reinigung der Wasserschlieren, DualBlock Anti-Verhedderungs-Design, Dynamische 3D-Anzeige | Filtertyp: HEPA Filter | Oberflächenempfehlung: Beton, Harter Boden, Hartholz, Holzwerkstoffe, Keramikfliese | Stromquelle: Batteriebetrieben</t>
+  </si>
+  <si>
+    <t>Tineco</t>
+  </si>
+  <si>
+    <t>https://www.amazon.de/stores/Tineco/page/7C365934-3A47-4B27-95CB-A4F47FAA26F6?lp_asin=B0DPP6C5YP&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto</t>
+  </si>
+  <si>
+    <t>Tineco Floor ONE S9 Artist Smart Nass-Trockensauger, SmoothDrive, DualBlock</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Elegantes und ästhetisches Design: S9 Artist Waschsauger ist von der Aurora Borealis inspiriert, vereint die Himmelstöne mit leuchtenden Aurora-Farben für eine natürlich schöne Wohnästhetik verbindet. Perfekt für designbewusste Haushalt.
+Unerreichte 22.000Pa Saugkraft und 50 Minuten Laufzeit: Erleben Sie eine tiefgehende Reinigung mit branchenführender Saugleistung und verlängerter Laufzeit für mühelose, unterbrechungsfreie Reinigung – ideal für große Wohnungen und Haushalte mit Haustieren.
+180° Lay-Flat &amp; ultra-schlankes Design (nur 12,85 cm): der Bodenreiniger kann mühelos unter Betten, Sofas und und Bereiche mit geringem Platzangebot gleichen, sodass kein Staub oder Haare zurückbleiben – perfekt für eine gründliche Reinigung.
+FlashDry-Selbstreinigungssystem für maximale Hygiene: Mit erhitztem Frischwasser werden Schmutz und Flecken von Rohr bis Bürstenwalze effektiv entfernt, anschließend trocknet 85°C heiße Luft jeden Teil der Maschine. Der Wischsauger verhindert unangenehme Gerüche, wirklich sorgenfrei nach dem Gebrauch.
+DualBlock Anti-Tangle-Design: Die doppelschichtigen Schaber verhindern das Verheddern und Verstopfen von Haaren, indem der Saugwischer die Haare mit einem Kammschaber einfangen und schmutziges Wasser und Haare mit einem geraden Schaber wegwischen.
+Kundenservice &amp; Support: 2-jährige Herstellergarantie, klare Rückgabe- und Garantiewege sowie schrittweise Anleitung zum Kundenservice. Bei Problemen kontaktieren Sie uns einfach – wir lösen alles schnell für Sie.</t>
   </si>
   <si>
     <t>https://www.amazon.de/dp/B0DPP6C5YP?psc=1</t>
   </si>
   <si>
-    <t>https://images-eu.ssl-images-amazon.com/images/I/61HEpMCMG9L._AC_UL300_SR300,200_.jpg</t>
+    <t>https://m.media-amazon.com/images/I/31d14GorfwL._AC_US600_.jpg</t>
+  </si>
+  <si>
+    <t>B0HFPXNLLM</t>
+  </si>
+  <si>
+    <t>4</t>
+  </si>
+  <si>
+    <t>50</t>
+  </si>
+  <si>
+    <t>2024-12-25</t>
+  </si>
+  <si>
+    <t>DE</t>
+  </si>
+  <si>
+    <t>Neuss 41460 DE</t>
+  </si>
+  <si>
+    <t>https://www.amazon.de/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A2QOI9TFEBV4J3</t>
+  </si>
+  <si>
+    <t>5,3 Kilogramm</t>
+  </si>
+  <si>
+    <t>5.30 kg</t>
+  </si>
+  <si>
+    <t>33 x 29.2 x 72.4 cm</t>
+  </si>
+  <si>
+    <t>33.00 x 29.20 x 72.40 cm</t>
+  </si>
+  <si>
+    <t>10 kg</t>
+  </si>
+  <si>
+    <t>10.00 kg</t>
+  </si>
+  <si>
+    <t>72 x 33 x 30 cm</t>
+  </si>
+  <si>
+    <t>72.00 x 33.00 x 30.00 cm</t>
   </si>
   <si>
     <t>B0FX2MMRK3</t>
   </si>
   <si>
-    <t>Tineco Floor ONE S9 Artist Steam Pro Smart Nass-Trockensauger, HyperSteams160 °C Dampfmopp für hartnäckige Flecken, 90 Min</t>
+    <t>Set name: S9 Artist Steam Pro</t>
+  </si>
+  <si>
+    <t>Marke: Tineco | Besonderes Merkmal: 160℃ HyperSteam Technologie, DualBlock Anti-Verhedderungsdesign, ReverseScrub Technologie, Ultralange Laufzeit, Zwei Trocknungsmodi für jeden Bedarf | Filtertyp: HEPA Filter | Oberflächenempfehlung: Harter Boden | Stromquelle: Batteriebetrieben</t>
+  </si>
+  <si>
+    <t>https://www.amazon.de/stores/Tineco/page/7C365934-3A47-4B27-95CB-A4F47FAA26F6?lp_asin=B0FX2MMRK3&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto</t>
+  </si>
+  <si>
+    <t>Tineco Floor ONE S9 Artist Steam Pro Smart Nass-Trockensauger, HyperSteam</t>
+  </si>
+  <si>
+    <t xml:space="preserve">160℃ HyperSteam Technologie: Die innovative Kesseltechnologie von Tineco erhitzt Dampf auf bis zu 160℃ und stellt sicher, dass die Austrittstemperatur nicht unter 99℃ fällt, wodurch hartnäckiges Fett und Schmutz effektiv gelöst werden.
+ReverseScrub Technologie: Die Umkehrung der Bürstenrolle auf Knopfdruck ermöglicht müheloses Entfernen hartUltralange Laufzeitnäckiger Flecken und sorgt für eine nahtlose und effiziente Reinigung.
+Ultralange Laufzeit: Ermöglicht eine komplette Hausreinigung mit nur einer Ladung. Bis zu 90 min* im ruhig-Modus. Bis zu 75 min* im automatisch-Modus in flacher Position.
+DualBlock Anti-Verhedderungsdesign: Doppellagige Abstreifer verhindern effektiv, dass sich Haare verheddern, halten das Gerät verstopfungsfrei und sorgen für eine reibungslose, unterbrechungsfreie Reinigung.
+Zwei Trocknungsmodi für jeden Bedarf: Der FlashDry-Modus sorgt für schnelles Trocknen in beschäftigten Haushalten, während SilentDry mit ruhigen ≤45* dB(A) für eine friedliche Reinigung arbeitet.</t>
   </si>
   <si>
     <t>https://www.amazon.de/dp/B0FX2MMRK3?psc=1</t>
   </si>
   <si>
-    <t>https://images-eu.ssl-images-amazon.com/images/I/71qYMu5c95L._AC_UL300_SR300,200_.jpg</t>
+    <t>https://images-na.ssl-images-amazon.com/images/I/71qYMu5c95L._AC_US600_.jpg</t>
+  </si>
+  <si>
+    <t>B0HFN25V8Q</t>
+  </si>
+  <si>
+    <t>5</t>
+  </si>
+  <si>
+    <t>2025-10-22</t>
+  </si>
+  <si>
+    <t>10,8 Kilograms</t>
+  </si>
+  <si>
+    <t>10.80 kg</t>
+  </si>
+  <si>
+    <t>23.3 x 26.7 x 110.2 cm</t>
+  </si>
+  <si>
+    <t>23.30 x 26.70 x 110.20 cm</t>
+  </si>
+  <si>
+    <t>10.8 kg</t>
+  </si>
+  <si>
+    <t>72 x 32.4 x 28.8 cm</t>
+  </si>
+  <si>
+    <t>72.00 x 32.40 x 28.80 cm</t>
   </si>
   <si>
     <t>B0H62W3T31</t>
   </si>
   <si>
-    <t>ATEC Clean Nass Trockensauger &amp; Saugwischer Kabellos [Tierhaar-Anti-verheddern &amp; selbstreinigend] Akku-Staubsauger mit Wischf</t>
+    <t>Marke: ATEC Clean | Besonderes Merkmal: 35 min lange Laufzeit, Anti-Haarverfangungs-Technologie, Elektrolysiertes Wasser, Hohe Leistung, Selbstfahrend | Filtertyp: HEPA Filter | Oberflächenempfehlung: Harter Boden | Stromquelle: Batteriebetrieben</t>
+  </si>
+  <si>
+    <t>ATEC Clean</t>
+  </si>
+  <si>
+    <t>https://www.amazon.de/s/ref=bl_dp_s_web_0?ie=UTF8&amp;search-type=ss&amp;index=kitchen-de&amp;field-keywords=ATEC+Clean</t>
+  </si>
+  <si>
+    <t>Nass Trockensauger &amp; Saugwischer Kabellos [Tierhaar-Anti-verheddern &amp; selbstreinigend] Akku-Staubsauger mit Wischfunktion | 17.000 Pa | Nasssauger, Waschsauger, Wischsauger Gerät (DualPro)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">✅ SAUGEN &amp; WISCHEN IN EINEM ZUG Kaffeesatz, Rotwein, Pfotenabdrücke und Tierhaare in einem Lauf entfernen ohne Gerätewechsel: Ein Durchgang, makellos saubere Hartböden. So spart das 4 kg leichte Gerät täglich wertvolle Zeit.
+✅ ANTI-VERHEDDERUNGSSYSTEM Verhindert, dass sich Haare, Tierhaare und Fasern um die Bürstenrolle wickeln. Stattdessen werden sie direkt in den Schmutzbehälter aufgenommen – kein manuelles Entfernen, kein lästiges Entwirren.
+✅ SELBSTREINIGUNG + HEIßLUFTTROCKNUNG Einfach in die Reinigungsstation stellen und per Knopfdruck die automatische Reinigung starten. Die anschließende Warmlufttrocknung hält die Bürste sauber, trocken und geruchsfrei. Keine Schimmelbildung, keine muffigen Gerüche.
+✅ RANDLOS, FLACH &amp; LEICHT Eine beidseitige Kantenbürste reinigt bis zur Fußleiste ohne Wenden, 180°-Neigung ermöglicht Putzen unter Sofa &amp; Bett. Getrennte 600ml-Tanks für Frisch- &amp; Schmutzwasser sorgen für echte Hygiene.
+✅ BIS ZU 200 QM MIT EINER AKKULADUNG Reicht für die gesamte Wohnung in einem Rutsch. Premium-Qualität eines deutschen Unternehmens, entwickelt für Familien mit Kindern und Haustieren. Auspacken, Akku einsetzen, loslegen.
+✅ELECTROLYZED WATER FUNKTION Chemiefrei und Umweltfreundlich, Mit nur Leitungswasser erzeugt der DualPro durch Elektrolyse ein natürliches, desinfizierendes Reinigungswasser. So entfernen Sie Keime und Schmutz ohne chemische Zusätze – ideal für Familien, Haustiere und umweltbewusste Haushalte.</t>
   </si>
   <si>
     <t>https://www.amazon.de/dp/B0H62W3T31?psc=1</t>
   </si>
   <si>
-    <t>https://images-eu.ssl-images-amazon.com/images/I/81UYR2XHqKL._AC_UL300_SR300,200_.jpg</t>
+    <t>https://m.media-amazon.com/images/I/41Z9+MKiOKL._AC_US200_.jpg</t>
+  </si>
+  <si>
+    <t>6</t>
+  </si>
+  <si>
+    <t>4 Kilogramm</t>
+  </si>
+  <si>
+    <t>4.00 kg</t>
   </si>
   <si>
     <t>B0FN46V7CN</t>
   </si>
   <si>
-    <t>EUREKA FloorShine 880 Nass Trockensauger Akku, 24 kPa Kabelloser Staubsauger mit Wischfunktion, 100°C Selbstreinigung, 5-Min-</t>
+    <t>Marke: EUREKA | Besonderes Merkmal: 100° Selbstreinigender Nass-/Trockensauger, 60 Minuten Laufzeit und Dual-Assist-Antrieb, Dreifache Kantenreinigung und Anti-Wickel-Technologie, Smart DirtSense | Filtertyp: HEPA Filter | Oberflächenempfehlung: Alle Etagen | Stromquelle: Batteriebetrieben</t>
+  </si>
+  <si>
+    <t>EUREKA</t>
+  </si>
+  <si>
+    <t>https://www.amazon.de/stores/Eureka/page/4ABB8AC3-B138-4CAB-9371-548936230037?lp_asin=B0FN46V7CN&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto&amp;bl_grd_status=override</t>
+  </si>
+  <si>
+    <t>EUREKA FloorShine 880 Nass Trockensauger Akku, 24 kPa Kabelloser Staubsauger mit Wischfunktion, 100°C Selbstreinigung, 5-Min-Trocknung, Anti-Tangle, 3-seitig Kantenreinigung, 180° Flach Saugwischer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">【Leistungsstarke &amp; Mühelose Reinigung】: Mit einer Saugleistung von 24,000 Pa saugt der Eureka FloorShine 880 Saugwischer Kabellos hartnäckige Flecken vom Boden effektiv auf und erzielt einen "Clean-as-you-go"-Effekt. Das 180° Flachliege-Design mit nur 13 cm Höhe und 90° Schwenkradius gleitet mühelos unter Sofas, Betten und Schränke für eine gründliche Reinigung.
+【100° Selbstreinigender Nass Trockensauger】: Heißwasserspülung bei 100 °C löst jedes Schmutzpartikel, gefolgt von einer 5-minütigen Turbo-Lufttrocknung für eine flauschige, trockene und frisch duftende Rolle. Der FloorShine 880 akku staubsauger mit wischfunktion revolutioniert mit einer integrierten Odor-Lock-Kapsel im Schmutzwassertank, die geruchsverursachende Bakterien eine ganze Woche lang fernhält.
+【60 Minuten Laufzeit und Dual-Assist-Antrieb】: Mit erweiterten 6*4000 mAh ermöglicht der Staubsauger und Wischer in einem 60 Minuten ununterbrochene Reinigung. Der Dual-Assist-Antrieb und die Bürstenkopfbeleuchtung gewährleisten 100% müheloses Behandlung.
+【Dreifache Kantenreinigung und Anti-Wickel-Technologie】: Die Rollbürste des FloorShine 880 nass und trockensauger kabellos passt sich eng an Möbelkanten und schmale Spalten an, für eine lückenlose Reinigung ohne vernachlässigte Ecken. Die Anti-Tangle 3.0-Kammzahnbürste verhindert Haarwickel und garantierte streifenfreie Ergebnisse bei jeder Reinigung.
+【Smart DirtSense und 110 ML Reinigungsmitteltank】: Der Eureka FloorShine 880 Wischsauger kabellos mit akku erkennt intelligent den Schmutz, passt automatisch die Schrubbleistung an und gibt die perfekte Menge an Reinigungslösung ab für ein wahrhaftes rückstandsloses Ergebnis.</t>
   </si>
   <si>
     <t>https://www.amazon.de/dp/B0FN46V7CN?psc=1</t>
   </si>
   <si>
-    <t>https://images-eu.ssl-images-amazon.com/images/I/61pE-Rb8EaL._AC_UL300_SR300,200_.jpg</t>
+    <t>https://images-na.ssl-images-amazon.com/images/I/61pE-Rb8EaL._AC_US600_.jpg</t>
+  </si>
+  <si>
+    <t>7</t>
+  </si>
+  <si>
+    <t>2025-08-21</t>
+  </si>
+  <si>
+    <t>7,4 Kilogramm</t>
+  </si>
+  <si>
+    <t>7.40 kg</t>
+  </si>
+  <si>
+    <t>116 x 30.3 x 35.9 cm</t>
+  </si>
+  <si>
+    <t>116.00 x 30.30 x 35.90 cm</t>
+  </si>
+  <si>
+    <t>11.54 kg</t>
+  </si>
+  <si>
+    <t>78 x 35 x 33 cm</t>
+  </si>
+  <si>
+    <t>78.00 x 35.00 x 33.00 cm</t>
   </si>
   <si>
     <t>B0FR44ZBJP</t>
   </si>
   <si>
-    <t>Rowenta X-Clean 10, kabelloser Akku-Nass-Trockensauger, Saugwischer selbstreinigend und -trocknend, Nasssauger Ultraleicht: n</t>
+    <t>Farbe: Weiß</t>
+  </si>
+  <si>
+    <t>Marke: Rowenta | Besonderes Merkmal: 60 Minuten Laufzeit, Steuerung über LED-Bildschirm, selbstreinigendes und selbsttrocknendes System, ultraleicht: wiegt nur 0,8 kg in der Hand, verhedderungsfreier Mikrofaser-Roller | Filtertyp: Patrone | Oberflächenempfehlung: Harter Boden | Stromquelle: Batteriebetrieben</t>
+  </si>
+  <si>
+    <t>https://www.amazon.de/stores/Rowenta/page/F8BD1336-17F4-4FC9-B31C-02321E3AC422?lp_asin=B0FR44ZBJP&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto</t>
+  </si>
+  <si>
+    <t>Rowenta X-Clean 10, kabelloser Akku-Nass-Trockensauger, Saugwischer selbstreinigend und -trocknend, Nasssauger Ultraleicht: nur 0,8 kg in der Hand, Waschsauger mit 60 min Laufzeit, weiß, YY5785FE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Makellose Ergebnisse in kürzester Zeit: Ein Akku-Nass-Trockensauger, der in einem einzigen Arbeitsgang saugt und wischt, für eine zeitsparende All-in-One-Reinigungslösung
+Müheloses Staubsaugen: Selbstfahrendes Rollensystem von Narwal für ein ultraleichtes Reinigungserlebnis, das nur 0,8 kg in der Hand wiegt – mit einem flexiblen 180-Grad-Design
+Extra-lange Laufzeit: Laufzeit von bis zu 60 Minuten mit einer einzigen Ladung - ideal für unerwartete Verschmutzungen und eine gründliche Reinigung
+Selbstreinigungssystem: Exklusives, bidirektionales, selbstreinigendes und selbsttrocknendes System, das auf Knopfdruck angetrieben wird; für ein Gerät, das immer sauber, trocken und einsatzbereit ist
+Spitzentechnologie: Innovative Lösungen für eine leichtere, einschließlich Sprachunterstützung, benutzerfreundlicher Steuerungen über einen LED-Bildschirm, Echtzeit-Schmutzverfolgung und mehr</t>
   </si>
   <si>
     <t>https://www.amazon.de/dp/B0FR44ZBJP?psc=1</t>
   </si>
   <si>
-    <t>https://images-eu.ssl-images-amazon.com/images/I/61YVBi7d7CL._AC_UL300_SR300,200_.jpg</t>
+    <t>https://m.media-amazon.com/images/I/31da21x3JcL._AC_US600_.jpg</t>
+  </si>
+  <si>
+    <t>B0GPR921Z1</t>
+  </si>
+  <si>
+    <t>8</t>
+  </si>
+  <si>
+    <t>2025-09-22</t>
+  </si>
+  <si>
+    <t>4,15 Kilogramm</t>
+  </si>
+  <si>
+    <t>4.15 kg</t>
+  </si>
+  <si>
+    <t>23 x 27 x 116 cm</t>
+  </si>
+  <si>
+    <t>23.00 x 27.00 x 116.00 cm</t>
+  </si>
+  <si>
+    <t>6.56 kg</t>
+  </si>
+  <si>
+    <t>73.3 x 33.3 x 27.4 cm</t>
+  </si>
+  <si>
+    <t>73.30 x 33.30 x 27.40 cm</t>
+  </si>
+  <si>
+    <t>B0DGV9F4X3</t>
+  </si>
+  <si>
+    <t>Farbe: Dunkelgrau</t>
+  </si>
+  <si>
+    <t>Marke: Rowenta | Besonderes Merkmal: 2-in-1 Reinigung, LED Display, Nass/Trocken, Selbstreinigungssystem, automatische Schmutzerkennung, extra lange Laufzeit, intelligente Schmutzerkennung | Filtertyp: Schaumstofffilter, HEPA-Filter | Oberflächenempfehlung: Parkett, Marmor, Laminat, Fliesen | Stromquelle: Batteriebetrieben</t>
+  </si>
+  <si>
+    <t>https://www.amazon.de/stores/Rowenta/page/F8BD1336-17F4-4FC9-B31C-02321E3AC422?lp_asin=B0DGV9F4X3&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto</t>
+  </si>
+  <si>
+    <t>Rowenta X-Clean 4 kabelloser Nass- und Trockenstaubsauger, 2-in-1 Reinigung, 50 Min. Leistung, intelligente Schmutzerkennung, Selbstreinigungssystem, Dunkelgrau, GZ5037WO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2-IN-1-REINIGUNG: Ein kabelloser Nass- und Trockenstaubsauger, der zeitsparendes 2-in-1-Saugen und Wischen in einem einzigen Durchgang ermöglicht und so perfekte Ergebnisse auf allen Arten von Hartböden (Hartholz, Marmor, Laminat und Fliesen) erzielt
+INTELLIGENTE SCHMUTZERKENNUNG: Automatische Schmutzerkennung mit Farbindikatoren auf einem LED-Bildschirm - rot für schmutzig und blau für sauber - und automatische Anpassung der Rollendrehzahl/des Wasserdurchflusses für perfekte Ergebnisse
+EXTRA-LANGE LAUFZEIT: Kabellose Reinigung mit einer Laufzeit von bis zu 50 Minuten für eine Fläche von bis zu 350 m²* (*abhängig von der Wohnungseinrichtung)
+MÜHELOSES STAUBSAUGEN: Ein ultraleichtes Design mit einem selbstfahrenden Rollensystem für eine Reinigung, die nur 25% des Aufwands erfordert, sowie eine ausgefeilte Ergonomie und ein gut durchdachtes modernes Design
+LIEFERUMFANG: Rowenta X-Clean 4 kabelloser Nass- und Trockenstaubsauger, zusätzliche weiche Reinigungsrolle, Seitenbürste, Trocken- und Anti-Crash-Schaumfilter, Ladegerät, Lade- und Reinigungsstation, Reinigungsbürste</t>
+  </si>
+  <si>
+    <t>https://www.amazon.de/dp/B0DGV9F4X3?psc=1</t>
+  </si>
+  <si>
+    <t>https://m.media-amazon.com/images/I/31S3KICrUsL._AC_US600_.jpg</t>
+  </si>
+  <si>
+    <t>B0H7XLDTB1</t>
+  </si>
+  <si>
+    <t>9</t>
+  </si>
+  <si>
+    <t>2024-10-17</t>
+  </si>
+  <si>
+    <t>5,4 Kilogramm</t>
+  </si>
+  <si>
+    <t>5.40 kg</t>
+  </si>
+  <si>
+    <t>Sans fil Classique</t>
+  </si>
+  <si>
+    <t>7.52 kg</t>
+  </si>
+  <si>
+    <t>75.8 x 33 x 28.8 cm</t>
+  </si>
+  <si>
+    <t>75.80 x 33.00 x 28.80 cm</t>
   </si>
   <si>
     <t>B0G66NWWCR</t>
   </si>
   <si>
-    <t>Bosch Allzwecksauger PAS15-200sPAS15-200 (C)</t>
+    <t>Größe: 15L - 1000W</t>
+  </si>
+  <si>
+    <t>Marke: Bosch | Stromquelle: ac_dc | Enthaltene Komponenten: 2 x extension plastic pipes (2 608 001 217);Suction hose 2,0 m (2 608 001 213);Elbow pipe (2 608 001 210);Floor nozzle (2 608 001 211);Crevice nozzle (2 608 001 209);Paper bag (2 608 001 212);Cartridge filter (2 608 001 218);Kartonschachtel | Kabellos Ja/Nein?: Nein | Wattzahl: 1000 Watt</t>
+  </si>
+  <si>
+    <t>Bosch</t>
+  </si>
+  <si>
+    <t>https://www.amazon.de/stores/BoschDIY/page/17690673-38F2-4715-A4D6-6D23BC5AC7E6?lp_asin=B0G66NWWCR&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto</t>
+  </si>
+  <si>
+    <t>Bosch Allzwecksauger PAS15-200</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.000-W-Motor mit 200 mbar Saugleistung: entfernt mühelos nassen und trockenen Schmutz
+Kompaktes und leichtes Design: erleichtert den Transport und sorgt für effiziente Aufbewahrung
+Zubehör immer griffbereit: dank praktischer Aufbewahrung am Gerät
+Patronenfilter: entfernt nassen und trockenen Schmutz mit einem Filtersystem
+Lieferumfang: 2 x extension plastic pipes (2 608 001 217);Suction hose 2,0 m (2 608 001 213);Elbow pipe (2 608 001 210);Floor nozzle (2 608 001 211);Crevice nozzle (2 608 001 209);Paper bag (2 608 001 212);Cartridge filter (2 608 001 218);Kartonschachtel</t>
   </si>
   <si>
     <t>https://www.amazon.de/dp/B0G66NWWCR?psc=1</t>
   </si>
   <si>
-    <t>https://images-eu.ssl-images-amazon.com/images/I/61xEbwRg-HL._AC_UL300_SR300,200_.jpg</t>
-  </si>
-  <si>
-    <t>B0DGV9F4X3</t>
-  </si>
-  <si>
-    <t>Rowenta X-Clean 4 kabelloser Nass- und Trockenstaubsauger, 2-in-1 Reinigung, 50 Min. Leistung, intelligente Schmutzerkennung,</t>
-  </si>
-  <si>
-    <t>https://www.amazon.de/dp/B0DGV9F4X3?psc=1</t>
-  </si>
-  <si>
-    <t>https://images-eu.ssl-images-amazon.com/images/I/61w5mQfWH9L._AC_UL300_SR300,200_.jpg</t>
+    <t>https://m.media-amazon.com/images/W/BW_MEDIAX_AVIF_MEASUREMENT_1306696-T4/images/I/31ZFL7asYeL._AC_US600_.jpg</t>
+  </si>
+  <si>
+    <t>B0H6MY3KH1</t>
+  </si>
+  <si>
+    <t>10</t>
+  </si>
+  <si>
+    <t>2026-01-21</t>
+  </si>
+  <si>
+    <t>7,95 Kilograms</t>
+  </si>
+  <si>
+    <t>7.95 kg</t>
+  </si>
+  <si>
+    <t>49.9 x 40.1 x 37.9 cm</t>
+  </si>
+  <si>
+    <t>49.90 x 40.10 x 37.90 cm</t>
   </si>
   <si>
     <t>B0GL7P6391</t>
   </si>
   <si>
-    <t>JONR H2 PRO Nass-Trockensauger 20000 Pa, Heißwasser-Reinigung &amp; geruchsfreies Design, 1500ml Wassertank flachliegend 180°, un</t>
+    <t>Marke: JONR | Besonderes Merkmal: Duo-Clean | Filtertyp: Mehrstufiges Filtersystem | Oberflächenempfehlung: Alle Etagen | Stromquelle: Batteriebetrieben</t>
+  </si>
+  <si>
+    <t>JONR</t>
+  </si>
+  <si>
+    <t>https://www.amazon.de/stores/JONR/page/DAC39F39-859B-4414-BC57-D789ECE2CA82?lp_asin=B0GL7P6391&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto&amp;bl_grd_status=override</t>
+  </si>
+  <si>
+    <t>JONR H2 PRO Nass-Trockensauger 20000 Pa, Heißwasser-Reinigung &amp; geruchsfreies Design, 1500ml Wassertank flachliegend 180°, unverminderte Saug- &amp; Wasserleistung.</t>
+  </si>
+  <si>
+    <t>【Heißwasser-Selbstreinigung &amp; flexible Trocknung】Der JONR H2 PRO (2026) – Upgrade des H2 – bietet Heißwasser-Selbstreinigung zur gründlichen Entfernung hartnäckiger Flecken. Die flexible Trocknung (keine Hochgeschwindigkeitsrotation) schont den Motor und verlängert die Lebensdauer. Trocknungsrate: bis zu 90%.</t>
   </si>
   <si>
     <t>https://www.amazon.de/dp/B0GL7P6391?psc=1</t>
   </si>
   <si>
-    <t>https://images-eu.ssl-images-amazon.com/images/I/61KFErwK5aL._AC_UL300_SR300,200_.jpg</t>
+    <t>https://images-na.ssl-images-amazon.com/images/I/61KFErwK5aL._AC_US600_.jpg</t>
+  </si>
+  <si>
+    <t>11</t>
+  </si>
+  <si>
+    <t>2026-03-03</t>
+  </si>
+  <si>
+    <t>SpotZapper</t>
+  </si>
+  <si>
+    <t>CN</t>
+  </si>
+  <si>
+    <t>芜湖市 安徽省 241399 CN</t>
+  </si>
+  <si>
+    <t>https://www.amazon.de/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A17T2O4U8TIBEZ</t>
+  </si>
+  <si>
+    <t>7,9 Pfund</t>
+  </si>
+  <si>
+    <t>28 x 23 x 111 cm</t>
+  </si>
+  <si>
+    <t>28.00 x 23.00 x 111.00 cm</t>
+  </si>
+  <si>
+    <t>7.98 kg</t>
+  </si>
+  <si>
+    <t>61.7 x 34.5 x 33 cm</t>
+  </si>
+  <si>
+    <t>61.70 x 34.50 x 33.00 cm</t>
+  </si>
+  <si>
+    <t>B0FPMB88DH</t>
+  </si>
+  <si>
+    <t>Marke: EUREKA | Besonderes Merkmal: Anti-Tangle Pro, Einfache Bedienung und Pausenfunktion, Erweiterte Akkulaufzeit, Geräuscharmes Design, Größere Wassertanks, Hochtemperatur der Selbsttrocknung-Technologie, Innovatives Kantenreinigungsbürstendesign, Leicht zu verwenden, einfach zu manövrieren, Saugen und Wischen in einem Schritt, Selbsttrocknende Technologie, Sie können direkt nach dem Wischen barfuß laufen, Tiefsitzende Flecken lassen sich nicht mehr verstecken, Zwei Modi für jedes Reinigungsszenario | Filtertyp: HEPA Filter | Oberflächenempfehlung: Alle Etagen | Stromquelle: Batteriebetrieben</t>
+  </si>
+  <si>
+    <t>https://www.amazon.de/stores/Eureka/page/4ABB8AC3-B138-4CAB-9371-548936230037?lp_asin=B0FPMB88DH&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto&amp;bl_grd_status=override</t>
+  </si>
+  <si>
+    <t>EUREKA FloorShine 460 Nass Trockensauger Kabellos, 180° Flachdesign Wischsauger Saugwischer, 17000 Pa Akku Staubsauger mit Wischfunktion, 30min Laufzeit Reinigung unter tiefen Möbeln für HarteBoden</t>
+  </si>
+  <si>
+    <t xml:space="preserve">All-in-One Sauger &amp; Wischer: Dieser nass trockensauger akku entfernt flüssigen und festen Schmutz in einem Arbeitsgang. Als leistungsstarker Nass Trockensauger trocknet er so schnell, dass Sie sofort barfuß laufen können – der ideale kabelloser staubsauger mit wischfunktion für moderne Haushalte.
+Kraftvolle 4-in-1 Reinigungstechnologie: Unser nass und trockensauger kabellos kombiniert gleichmäßiges Sprühen, Hochgeschwindigkeits-Bürsten (495 U/min), effektives Abstreifen und starkes Absaugen (17 kPa) für eine gründliche, streifenfreie Reinigung in jeder Ecke.
+Innovatives Design für maximale Reinigung: Dieser nasssauger boden mit 180°-Flachliegedesign kann unter niedrigen Möbeln reinigen und spezielle Kantenbürste für perfekte Sauberkeit bis in die Raumecken.
+Hygienisch &amp; Wartungsfreundlich: Mit Anti-Haar-Wickel-System und Selbsttrocknungsfunktion. Dieser wischsauger saugwischer kabellos bietet maximale Hygiene ohne manuelles Reinigen der Bürste.
+Kabellose Freiheit &amp; Lange Laufzeit: Leicht, wendig und kabellos mit bis zu 30 Minuten kraftvoller Laufzeit. Der FloorShine 460 staubsauger nass und trocken verfügt über zwei große Wassertanks für längere Reinigungssitzungen: einen 600 ml Frischwassertank und einen 600 ml großen Schmutzwassertank, sodass Sie mit jeder Füllung mehr reinigen können.</t>
+  </si>
+  <si>
+    <t>https://www.amazon.de/dp/B0FPMB88DH?psc=1</t>
+  </si>
+  <si>
+    <t>https://images-na.ssl-images-amazon.com/images/I/71Veas8E33L._AC_US600_.jpg</t>
+  </si>
+  <si>
+    <t>12</t>
+  </si>
+  <si>
+    <t>2025-09-11</t>
+  </si>
+  <si>
+    <t>3,93 Kilogramm</t>
+  </si>
+  <si>
+    <t>3.93 kg</t>
+  </si>
+  <si>
+    <t>21.8 x 110.1 x 20 cm</t>
+  </si>
+  <si>
+    <t>21.80 x 110.10 x 20.00 cm</t>
+  </si>
+  <si>
+    <t>7.51 kg</t>
+  </si>
+  <si>
+    <t>76 x 31.6 x 26.8 cm</t>
+  </si>
+  <si>
+    <t>76.00 x 31.60 x 26.80 cm</t>
   </si>
   <si>
     <t>B0H8Y83NN7</t>
   </si>
   <si>
-    <t>Akku Nass-Trockensauger für Makita 18V Batterie, 18 kPa Werkstattsaugersmit HEPA-Filter, 10L Staubbehälter, Kabelloser Stau</t>
+    <t>Marke: UtaUla | Besonderes Merkmal: HEPA, Kabellos, Nass/Trocken, Tragbar | Filtertyp: HEPA Filter | Kabellos Ja/Nein?: Ja | Artikelgewicht: 2,6 Kilogramm</t>
+  </si>
+  <si>
+    <t>UtaUla</t>
+  </si>
+  <si>
+    <t>https://www.amazon.de/s/ref=bl_dp_s_web_0?ie=UTF8&amp;search-type=ss&amp;index=kitchen-de&amp;field-keywords=UtaUla</t>
+  </si>
+  <si>
+    <t>Akku Nass-Trockensauger für Makita 18V Batterie, 18 kPa Werkstattsauger</t>
+  </si>
+  <si>
+    <t xml:space="preserve">【Kompatibel mit Makita 18V Akku】Dieser Akku Nass-Trockensauger ist kompatibel mit Makita 18V Lithium-Ionen-Akkus wie BL1830, BL1830B, BL1840, BL1840B, BL1850, BL1850B und BL1860B. Die integrierten Schutzfunktionen gegen Unterspannung, Überlastung und Überhitzung unterstützen einen sicheren und zuverlässigen Betrieb. Hinweis: Akku und Ladegerät sind nicht im Lieferumfang enthalten. Nicht kompatibel mit G-Serie Akkus
+【3-in-1 Multifunktion】Der kabellose Nass- und Trockensauger kombiniert Trockensaugen, Nasssaugen und Blasfunktion in einem Gerät. Der leistungsstarke 150W Motor erzeugt eine Saugkraft von bis zu 18 kPa und einen Luftstrom von 40 CFM, wodurch Staub, Schmutz, Flüssigkeiten und kleine Partikel schnell entfernt werden können. Ideal für Garage, Werkstatt, Auto, Garten und Haushalt
+【10L großer Staubbehälter】Ausgestattet mit einem 10L großen Staubbehälter verringert dieser Akku Industriesauger die Häufigkeit des Entleerens und ermöglicht eine effiziente Reinigung über längere Zeit. Das leichte Design mit nur 2,6 kg, ergonomischem Griff und leichtgängigen drehbaren Rollen ermöglicht einen einfachen Transport und eine platzsparende Aufbewahrung
+【HEPA-Hochleistungsfiltersystem】Das integrierte HEPA-Filtersystem filtert bis zu 99,97 % der Feinstaubpartikel und hilft dabei, Staub während der Reinigung effektiv zurückzuhalten. Dadurch wird die Staubverteilung reduziert und eine sauberere Umgebung unterstützt. Der Nass-Trockensauger eignet sich besonders für Zuhause, Garage und Werkstatt, wo eine effektive Staubreinigung erforderlich ist
+【Vielseitige Anwendung】Mit flexiblem Saugschlauch, Fugendüse und Rundbürste eignet sich dieser Akku-Nass-Trockensauger für verschiedene Reinigungsaufgaben. Ob Bodenflächen, enge Bereiche im Auto, Möbelzwischenräume oder Werkstattbereiche – das kabellose Design ermöglicht eine flexible Nutzung ohne störendes Kabel. Ideal als praktischer Werkstattsauger für Zuhause, Garage, Auto und Werkstatt</t>
   </si>
   <si>
     <t>https://www.amazon.de/dp/B0H8Y83NN7?psc=1</t>
   </si>
   <si>
-    <t>https://images-eu.ssl-images-amazon.com/images/I/71Rk7RmZfuL._AC_UL300_SR300,200_.jpg</t>
-  </si>
-  <si>
-    <t>B0FPMB88DH</t>
-  </si>
-  <si>
-    <t>EUREKA FloorShine 460 Nass Trockensauger Kabellos, 180° Flachdesign Wischsauger Saugwischer, 17000 Pa Akku Staubsauger mit Wi</t>
-  </si>
-  <si>
-    <t>https://www.amazon.de/dp/B0FPMB88DH?psc=1</t>
-  </si>
-  <si>
-    <t>https://images-eu.ssl-images-amazon.com/images/I/71Veas8E33L._AC_UL300_SR300,200_.jpg</t>
+    <t>https://images-na.ssl-images-amazon.com/images/I/71Rk7RmZfuL._AC_US600_.jpg</t>
+  </si>
+  <si>
+    <t>13</t>
+  </si>
+  <si>
+    <t>2026-08-18</t>
+  </si>
+  <si>
+    <t>武汉市 湖北省 430064 CN</t>
+  </si>
+  <si>
+    <t>https://www.amazon.de/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A2TW0HFVR94W5Z</t>
+  </si>
+  <si>
+    <t>2,6 Kilogramm</t>
+  </si>
+  <si>
+    <t>2.60 kg</t>
+  </si>
+  <si>
+    <t>35 x 22 x 22 cm</t>
+  </si>
+  <si>
+    <t>35.00 x 22.00 x 22.00 cm</t>
+  </si>
+  <si>
+    <t>4 kg</t>
+  </si>
+  <si>
+    <t>39.5 x 26.5 x 2.6 cm</t>
+  </si>
+  <si>
+    <t>39.50 x 26.50 x 2.60 cm</t>
+  </si>
+  <si>
+    <t>标准包裹</t>
   </si>
   <si>
     <t>B0GX7CQRDX</t>
   </si>
   <si>
-    <t>MOVA M50 Nass- und Trockensauger, 22000 Pa Saugkraft, 85 °C Bürstenwäsche, 90° drehbares Design, intelligente Schmutzerkennun</t>
+    <t>Marke: MOVA | Besonderes Merkmal: Kabellos | Filtertyp: HEPA Filter | Oberflächenempfehlung: Harter Boden | Stromquelle: Batteriebetrieben</t>
+  </si>
+  <si>
+    <t>MOVA</t>
+  </si>
+  <si>
+    <t>https://www.amazon.de/stores/MOVA/page/C421873F-2042-459A-B673-3BA824983D27?lp_asin=B0GX7CQRDX&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto&amp;bl_grd_status=override</t>
+  </si>
+  <si>
+    <t>MOVA M50 Nass- und Trockensauger, 22000 Pa Saugkraft, 85 °C Bürstenwäsche, 90° drehbares Design, intelligente Schmutzerkennung, Saugkraftregulierung, 3 Jahre Garantie</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Starke Saugkraft und Unterdruck: Mit einer beeindruckenden Saugleistung von 22.000 Pa* bewältigt der M50 alle Verschmutzungen, die nass oder trocken, oberflächlich oder tief eindringen. Sie können auch bei hartnäckigsten Flecken einen Druck von ca. 20 N* nach unten ausüben, um Ihre Böden zu reiben.
+180° Vollneigungszugang mit nicht reduzierter Saugkraft: Die voll liegende Access-Technologie ermöglicht es dem Sauger, unter Möbeln von mindestens 14 cm vom Boden aus zu gelangen und gleichzeitig seine volle Saugkraft für eine gründliche Reinigung in schwer zugänglichen Bereichen beizubehalten.
+Schluss mit Haarverwicklungen: Der häufige Zahnschaberkamm hinterlässt praktisch keine Haarsträhnen mit seinen dichten Kammzähne an der Seite der Bürste und verbessert die Sammeleffizienz. Es kann selbst feinste Tierhaare effektiv erfassen, verhindert Verwicklungen.
+Lückenfrei* Doppelte Kantenreinigung: Die zweischneidige Bürste ist für eine überlegene Leistung in engen Räumen konzipiert und entfernt Staub und Schmutz bis zu 0 mm*, indem sie Kanten wie Wände und Sockelleisten meistern.
+Intelligente Schmutzerkennung und Einstellung der Saugkraft: Der M50 ist mit einem Schmutzsensor ausgestattet, der sowohl die Art als auch das Niveau des Schmutzes erkennt. Im Smart-Modus passt er die Saugleistung und den Wasserauslass automatisch an, für eine optimale Reinigungseffizienz, je nach Erkennung.</t>
   </si>
   <si>
     <t>https://www.amazon.de/dp/B0GX7CQRDX?psc=1</t>
   </si>
   <si>
-    <t>https://images-eu.ssl-images-amazon.com/images/I/611qVIQFvkL._AC_UL300_SR300,200_.jpg</t>
+    <t>https://images-na.ssl-images-amazon.com/images/I/611qVIQFvkL._AC_US600_.jpg</t>
+  </si>
+  <si>
+    <t>14</t>
+  </si>
+  <si>
+    <t>2026-05-18</t>
+  </si>
+  <si>
+    <t>Schnäppchen Schuppen</t>
+  </si>
+  <si>
+    <t>CZ</t>
+  </si>
+  <si>
+    <t>Ostrava Moravskoslezsky 703 00 CZ</t>
+  </si>
+  <si>
+    <t>https://www.amazon.de/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A3TSTGWB8M3T3Z</t>
+  </si>
+  <si>
+    <t>7,8 Kilograms</t>
+  </si>
+  <si>
+    <t>7.80 kg</t>
+  </si>
+  <si>
+    <t>32 x 33.2 x 124 cm</t>
+  </si>
+  <si>
+    <t>32.00 x 33.20 x 124.00 cm</t>
+  </si>
+  <si>
+    <t>7.8 kg</t>
+  </si>
+  <si>
+    <t>75 x 38.7 x 34.5 cm</t>
+  </si>
+  <si>
+    <t>75.00 x 38.70 x 34.50 cm</t>
   </si>
   <si>
     <t>B0BJ7SZ1W1</t>
   </si>
   <si>
+    <t>Marke: KÄRCHER | Besonderes Merkmal: Kompakt | Filtertyp: HEPA Filter | Oberflächenempfehlung: Alle Etagen | Stromquelle: Kabelgebunden</t>
+  </si>
+  <si>
+    <t>KÄRCHER</t>
+  </si>
+  <si>
+    <t>https://www.amazon.de/stores/K%C3%A4rcher/page/EFE3653A-1163-432C-A85B-0486A31C0E3D?lp_asin=B0BJ7SZ1W1&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto</t>
+  </si>
+  <si>
     <t>KWD 3 S V-17/4/20/F</t>
   </si>
   <si>
+    <t>Kompakt</t>
+  </si>
+  <si>
     <t>https://www.amazon.de/dp/B0BJ7SZ1W1?psc=1</t>
   </si>
   <si>
-    <t>https://images-eu.ssl-images-amazon.com/images/I/51ZkjjdFteL._AC_UL300_SR300,200_.jpg</t>
+    <t>https://m.media-amazon.com/images/I/31m5B2TrvrL._AC_US200_.jpg</t>
+  </si>
+  <si>
+    <t>15</t>
+  </si>
+  <si>
+    <t>6,5 Kilogramm</t>
+  </si>
+  <si>
+    <t>6.50 kg</t>
   </si>
   <si>
     <t>导出时自动对相同ASIN去重。可能导致导出的产品总数与页面显示数量不一致</t>
@@ -425,9 +1123,6 @@
   </si>
   <si>
     <t>市场份额</t>
-  </si>
-  <si>
-    <t>未知品牌</t>
   </si>
   <si>
     <t>卖家</t>
@@ -602,6 +1297,9 @@
     <xf numFmtId="3" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="4" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
     <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
@@ -609,9 +1307,6 @@
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="4" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -669,13 +1364,13 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>192000</xdr:colOff>
-      <xdr:row>1</xdr:row>
+      <xdr:row>3</xdr:row>
       <xdr:rowOff>44999</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
       <xdr:colOff>428799</xdr:colOff>
-      <xdr:row>1</xdr:row>
+      <xdr:row>3</xdr:row>
       <xdr:rowOff>270000</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -713,13 +1408,13 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>192000</xdr:colOff>
-      <xdr:row>3</xdr:row>
+      <xdr:row>2</xdr:row>
       <xdr:rowOff>44999</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
       <xdr:colOff>428799</xdr:colOff>
-      <xdr:row>3</xdr:row>
+      <xdr:row>2</xdr:row>
       <xdr:rowOff>270000</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -757,13 +1452,13 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>192000</xdr:colOff>
-      <xdr:row>2</xdr:row>
+      <xdr:row>1</xdr:row>
       <xdr:rowOff>44999</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
       <xdr:colOff>428799</xdr:colOff>
-      <xdr:row>2</xdr:row>
+      <xdr:row>1</xdr:row>
       <xdr:rowOff>270000</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -801,13 +1496,13 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>192000</xdr:colOff>
-      <xdr:row>5</xdr:row>
+      <xdr:row>4</xdr:row>
       <xdr:rowOff>45000</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
       <xdr:colOff>428799</xdr:colOff>
-      <xdr:row>5</xdr:row>
+      <xdr:row>4</xdr:row>
       <xdr:rowOff>270000</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -845,13 +1540,13 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>192000</xdr:colOff>
-      <xdr:row>4</xdr:row>
+      <xdr:row>5</xdr:row>
       <xdr:rowOff>45000</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
       <xdr:colOff>428799</xdr:colOff>
-      <xdr:row>4</xdr:row>
+      <xdr:row>5</xdr:row>
       <xdr:rowOff>270000</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -889,13 +1584,13 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>192000</xdr:colOff>
-      <xdr:row>7</xdr:row>
+      <xdr:row>6</xdr:row>
       <xdr:rowOff>45000</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
       <xdr:colOff>428799</xdr:colOff>
-      <xdr:row>7</xdr:row>
+      <xdr:row>6</xdr:row>
       <xdr:rowOff>270000</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -933,13 +1628,13 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>192000</xdr:colOff>
-      <xdr:row>6</xdr:row>
+      <xdr:row>7</xdr:row>
       <xdr:rowOff>45000</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
       <xdr:colOff>428799</xdr:colOff>
-      <xdr:row>6</xdr:row>
+      <xdr:row>7</xdr:row>
       <xdr:rowOff>270000</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -1197,13 +1892,13 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>192000</xdr:colOff>
-      <xdr:row>13</xdr:row>
+      <xdr:row>14</xdr:row>
       <xdr:rowOff>45000</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
       <xdr:colOff>428799</xdr:colOff>
-      <xdr:row>13</xdr:row>
+      <xdr:row>14</xdr:row>
       <xdr:rowOff>270000</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -1241,13 +1936,13 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>192000</xdr:colOff>
-      <xdr:row>14</xdr:row>
+      <xdr:row>13</xdr:row>
       <xdr:rowOff>45000</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
       <xdr:colOff>428799</xdr:colOff>
-      <xdr:row>14</xdr:row>
+      <xdr:row>13</xdr:row>
       <xdr:rowOff>270000</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -1962,7 +2657,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="2" ht="24" customHeight="1" spans="1:69" x14ac:dyDescent="0.25">
+    <row r="2" ht="24" customHeight="1" spans="1:70" x14ac:dyDescent="0.25">
       <c r="A2" s="13">
         <v>1</v>
       </c>
@@ -1973,145 +2668,197 @@
         <v>71</v>
       </c>
       <c r="D2" s="14" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="E2" s="14" t="s">
-        <v>70</v>
+        <v>73</v>
+      </c>
+      <c r="F2" s="14" t="s">
+        <v>74</v>
       </c>
       <c r="G2" s="14" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="H2" s="14" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="I2" s="14" t="s">
-        <v>70</v>
+        <v>77</v>
       </c>
       <c r="J2" s="14" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="K2" s="14" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="L2" s="14" t="s">
-        <v>71</v>
-      </c>
-      <c r="M2" s="1"/>
+        <v>80</v>
+      </c>
+      <c r="M2" s="14" t="s">
+        <v>81</v>
+      </c>
       <c r="N2" s="14" t="s">
-        <v>70</v>
-      </c>
-      <c r="O2" s="15" t="s">
-        <v>70</v>
-      </c>
-      <c r="P2" s="15" t="s">
-        <v>70</v>
-      </c>
-      <c r="Q2" s="16" t="s">
-        <v>70</v>
+        <v>82</v>
+      </c>
+      <c r="O2" s="15">
+        <v>658</v>
+      </c>
+      <c r="P2" s="15">
+        <v>-390</v>
+      </c>
+      <c r="Q2" s="16">
+        <v>-4.48</v>
       </c>
       <c r="R2" s="17" t="s">
-        <v>70</v>
+        <v>83</v>
       </c>
       <c r="S2" s="18" t="s">
-        <v>70</v>
-      </c>
-      <c r="T2" s="15" t="s">
-        <v>70</v>
-      </c>
-      <c r="U2" s="16" t="s">
-        <v>70</v>
-      </c>
-      <c r="V2" s="15" t="s">
-        <v>70</v>
+        <v>84</v>
+      </c>
+      <c r="T2" s="15">
+        <v>5930</v>
+      </c>
+      <c r="U2" s="16">
+        <v>0.08</v>
+      </c>
+      <c r="V2" s="15">
+        <v>1126581</v>
       </c>
       <c r="W2" s="15" t="s">
-        <v>70</v>
-      </c>
-      <c r="X2" s="15" t="s">
-        <v>70</v>
-      </c>
-      <c r="Z2" s="4"/>
+        <v>85</v>
+      </c>
+      <c r="X2" s="15">
+        <v>189980</v>
+      </c>
+      <c r="Y2" s="19">
+        <v>6</v>
+      </c>
+      <c r="Z2" s="20">
+        <v>189.98</v>
+      </c>
+      <c r="AA2" s="4"/>
+      <c r="AB2" s="1"/>
+      <c r="AC2" s="2"/>
       <c r="AD2" s="19">
+        <v>100</v>
+      </c>
+      <c r="AE2" s="15">
+        <v>184</v>
+      </c>
+      <c r="AF2" s="21">
+        <v>4.5</v>
+      </c>
+      <c r="AG2" s="22">
+        <v>0.031</v>
+      </c>
+      <c r="AH2" s="20">
+        <v>7.31</v>
+      </c>
+      <c r="AI2" s="16">
+        <v>0.81</v>
+      </c>
+      <c r="AK2" s="13" t="s">
+        <v>86</v>
+      </c>
+      <c r="AL2" s="19">
+        <v>161</v>
+      </c>
+      <c r="AM2" s="13" t="s">
+        <v>87</v>
+      </c>
+      <c r="AN2" s="13" t="s">
+        <v>70</v>
+      </c>
+      <c r="AO2" s="13" t="s">
+        <v>70</v>
+      </c>
+      <c r="AP2" s="4"/>
+      <c r="AQ2" s="19">
+        <v>10</v>
+      </c>
+      <c r="AR2" s="19">
+        <v>2</v>
+      </c>
+      <c r="AS2" s="14" t="s">
+        <v>88</v>
+      </c>
+      <c r="AT2" s="13" t="s">
+        <v>87</v>
+      </c>
+      <c r="AU2" s="13" t="s">
+        <v>70</v>
+      </c>
+      <c r="AV2" s="14" t="s">
+        <v>70</v>
+      </c>
+      <c r="AW2" s="13" t="s">
+        <v>70</v>
+      </c>
+      <c r="AX2" s="13" t="s">
+        <v>89</v>
+      </c>
+      <c r="AY2" s="13" t="s">
+        <v>89</v>
+      </c>
+      <c r="AZ2" s="13" t="s">
+        <v>70</v>
+      </c>
+      <c r="BA2" s="13" t="s">
+        <v>70</v>
+      </c>
+      <c r="BB2" s="13" t="s">
+        <v>70</v>
+      </c>
+      <c r="BC2" s="13" t="s">
+        <v>89</v>
+      </c>
+      <c r="BD2" s="13" t="s">
+        <v>89</v>
+      </c>
+      <c r="BE2" s="13" t="s">
+        <v>70</v>
+      </c>
+      <c r="BF2" s="13" t="s">
+        <v>89</v>
+      </c>
+      <c r="BG2" s="13" t="s">
+        <v>70</v>
+      </c>
+      <c r="BH2" s="14" t="s">
+        <v>70</v>
+      </c>
+      <c r="BI2" s="23" t="s">
+        <v>90</v>
+      </c>
+      <c r="BJ2" s="23" t="s">
+        <v>91</v>
+      </c>
+      <c r="BK2" s="23" t="s">
+        <v>70</v>
+      </c>
+      <c r="BL2" s="23" t="s">
+        <v>92</v>
+      </c>
+      <c r="BM2" s="23" t="s">
+        <v>93</v>
+      </c>
+      <c r="BN2" s="23" t="s">
+        <v>94</v>
+      </c>
+      <c r="BO2" s="23" t="s">
+        <v>94</v>
+      </c>
+      <c r="BP2" s="23" t="s">
+        <v>95</v>
+      </c>
+      <c r="BQ2" s="23" t="s">
+        <v>96</v>
+      </c>
+      <c r="BR2" s="13" t="s">
         <v>97</v>
       </c>
-      <c r="AF2" s="20">
-        <v>4.4</v>
-      </c>
-      <c r="AG2" s="21">
-        <v>0</v>
-      </c>
-      <c r="AI2" s="16">
-        <v>0</v>
-      </c>
-      <c r="AK2" s="1"/>
-      <c r="AL2" s="19" t="s">
-        <v>70</v>
-      </c>
-      <c r="AN2" s="13" t="s">
-        <v>70</v>
-      </c>
-      <c r="AO2" s="13" t="s">
-        <v>70</v>
-      </c>
-      <c r="AQ2" s="19" t="s">
-        <v>70</v>
-      </c>
-      <c r="AU2" s="13" t="s">
-        <v>70</v>
-      </c>
-      <c r="AV2" s="14" t="s">
-        <v>70</v>
-      </c>
-      <c r="AW2" s="13" t="s">
-        <v>70</v>
-      </c>
-      <c r="AX2" s="13" t="s">
-        <v>70</v>
-      </c>
-      <c r="AY2" s="13" t="s">
-        <v>70</v>
-      </c>
-      <c r="AZ2" s="13" t="s">
-        <v>70</v>
-      </c>
-      <c r="BA2" s="13" t="s">
-        <v>70</v>
-      </c>
-      <c r="BB2" s="13" t="s">
-        <v>70</v>
-      </c>
-      <c r="BC2" s="13" t="s">
-        <v>70</v>
-      </c>
-      <c r="BD2" s="13" t="s">
-        <v>70</v>
-      </c>
-      <c r="BE2" s="13" t="s">
-        <v>70</v>
-      </c>
-      <c r="BF2" s="13" t="s">
-        <v>70</v>
-      </c>
-      <c r="BG2" s="13" t="s">
-        <v>70</v>
-      </c>
-      <c r="BH2" s="14" t="s">
-        <v>70</v>
-      </c>
-      <c r="BK2" s="22" t="s">
-        <v>70</v>
-      </c>
-      <c r="BM2" s="22" t="s">
-        <v>70</v>
-      </c>
-      <c r="BO2" s="22" t="s">
-        <v>70</v>
-      </c>
-      <c r="BQ2" s="22" t="s">
-        <v>70</v>
-      </c>
     </row>
-    <row r="3" ht="24" customHeight="1" spans="1:69" x14ac:dyDescent="0.25">
+    <row r="3" ht="24" customHeight="1" spans="1:70" x14ac:dyDescent="0.25">
       <c r="A3" s="13">
         <v>2</v>
       </c>
@@ -2119,59 +2866,64 @@
         <v>70</v>
       </c>
       <c r="C3" s="14" t="s">
-        <v>76</v>
+        <v>98</v>
       </c>
       <c r="D3" s="14" t="s">
-        <v>70</v>
+        <v>99</v>
       </c>
       <c r="E3" s="14" t="s">
-        <v>70</v>
+        <v>100</v>
+      </c>
+      <c r="F3" s="14" t="s">
+        <v>101</v>
       </c>
       <c r="G3" s="14" t="s">
-        <v>72</v>
+        <v>102</v>
       </c>
       <c r="H3" s="14" t="s">
-        <v>77</v>
+        <v>103</v>
       </c>
       <c r="I3" s="14" t="s">
-        <v>70</v>
+        <v>104</v>
       </c>
       <c r="J3" s="14" t="s">
-        <v>78</v>
+        <v>105</v>
       </c>
       <c r="K3" s="14" t="s">
-        <v>79</v>
+        <v>106</v>
       </c>
       <c r="L3" s="14" t="s">
-        <v>76</v>
-      </c>
-      <c r="M3" s="1"/>
+        <v>107</v>
+      </c>
+      <c r="M3" s="14" t="s">
+        <v>81</v>
+      </c>
       <c r="N3" s="14" t="s">
-        <v>70</v>
-      </c>
-      <c r="O3" s="15" t="s">
-        <v>70</v>
-      </c>
-      <c r="P3" s="15" t="s">
-        <v>70</v>
-      </c>
-      <c r="Q3" s="16" t="s">
-        <v>70</v>
+        <v>82</v>
+      </c>
+      <c r="O3" s="15">
+        <v>6036</v>
+      </c>
+      <c r="P3" s="15">
+        <v>4154</v>
+      </c>
+      <c r="Q3" s="16">
+        <v>0.45</v>
       </c>
       <c r="R3" s="17" t="s">
-        <v>70</v>
+        <v>83</v>
       </c>
       <c r="S3" s="18" t="s">
-        <v>70</v>
-      </c>
-      <c r="T3" s="15" t="s">
-        <v>70</v>
-      </c>
-      <c r="U3" s="16" t="s">
-        <v>70</v>
-      </c>
-      <c r="V3" s="15" t="s">
-        <v>70</v>
+        <v>108</v>
+      </c>
+      <c r="T3" s="15">
+        <v>637</v>
+      </c>
+      <c r="U3" s="16">
+        <v>0.22</v>
+      </c>
+      <c r="V3" s="15">
+        <v>129247</v>
       </c>
       <c r="W3" s="15" t="s">
         <v>70</v>
@@ -2179,22 +2931,41 @@
       <c r="X3" s="15" t="s">
         <v>70</v>
       </c>
-      <c r="Z3" s="4"/>
+      <c r="Y3" s="19">
+        <v>5</v>
+      </c>
+      <c r="Z3" s="20">
+        <v>202.9</v>
+      </c>
+      <c r="AA3" s="4"/>
+      <c r="AB3" s="1"/>
+      <c r="AC3" s="2"/>
       <c r="AD3" s="19">
-        <v>2740</v>
-      </c>
-      <c r="AF3" s="20">
+        <v>2745</v>
+      </c>
+      <c r="AE3" s="15">
+        <v>0</v>
+      </c>
+      <c r="AF3" s="21">
         <v>4.3</v>
       </c>
-      <c r="AG3" s="21">
+      <c r="AG3" s="22">
         <v>0</v>
       </c>
+      <c r="AH3" s="20">
+        <v>7.68</v>
+      </c>
       <c r="AI3" s="16">
-        <v>0</v>
-      </c>
-      <c r="AK3" s="1"/>
-      <c r="AL3" s="19" t="s">
-        <v>70</v>
+        <v>0.81</v>
+      </c>
+      <c r="AK3" s="13" t="s">
+        <v>109</v>
+      </c>
+      <c r="AL3" s="19">
+        <v>369</v>
+      </c>
+      <c r="AM3" s="13" t="s">
+        <v>87</v>
       </c>
       <c r="AN3" s="13" t="s">
         <v>70</v>
@@ -2202,8 +2973,18 @@
       <c r="AO3" s="13" t="s">
         <v>70</v>
       </c>
-      <c r="AQ3" s="19" t="s">
-        <v>70</v>
+      <c r="AP3" s="4"/>
+      <c r="AQ3" s="19">
+        <v>10</v>
+      </c>
+      <c r="AR3" s="19">
+        <v>2</v>
+      </c>
+      <c r="AS3" s="14" t="s">
+        <v>88</v>
+      </c>
+      <c r="AT3" s="13" t="s">
+        <v>87</v>
       </c>
       <c r="AU3" s="13" t="s">
         <v>70</v>
@@ -2218,7 +2999,7 @@
         <v>70</v>
       </c>
       <c r="AY3" s="13" t="s">
-        <v>70</v>
+        <v>89</v>
       </c>
       <c r="AZ3" s="13" t="s">
         <v>70</v>
@@ -2230,16 +3011,16 @@
         <v>70</v>
       </c>
       <c r="BC3" s="13" t="s">
-        <v>70</v>
+        <v>89</v>
       </c>
       <c r="BD3" s="13" t="s">
-        <v>70</v>
+        <v>89</v>
       </c>
       <c r="BE3" s="13" t="s">
         <v>70</v>
       </c>
       <c r="BF3" s="13" t="s">
-        <v>70</v>
+        <v>89</v>
       </c>
       <c r="BG3" s="13" t="s">
         <v>70</v>
@@ -2247,20 +3028,38 @@
       <c r="BH3" s="14" t="s">
         <v>70</v>
       </c>
-      <c r="BK3" s="22" t="s">
-        <v>70</v>
-      </c>
-      <c r="BM3" s="22" t="s">
-        <v>70</v>
-      </c>
-      <c r="BO3" s="22" t="s">
-        <v>70</v>
-      </c>
-      <c r="BQ3" s="22" t="s">
-        <v>70</v>
+      <c r="BI3" s="23" t="s">
+        <v>90</v>
+      </c>
+      <c r="BJ3" s="23" t="s">
+        <v>110</v>
+      </c>
+      <c r="BK3" s="23" t="s">
+        <v>111</v>
+      </c>
+      <c r="BL3" s="23" t="s">
+        <v>112</v>
+      </c>
+      <c r="BM3" s="23" t="s">
+        <v>113</v>
+      </c>
+      <c r="BN3" s="23" t="s">
+        <v>114</v>
+      </c>
+      <c r="BO3" s="23" t="s">
+        <v>115</v>
+      </c>
+      <c r="BP3" s="23" t="s">
+        <v>116</v>
+      </c>
+      <c r="BQ3" s="23" t="s">
+        <v>117</v>
+      </c>
+      <c r="BR3" s="13" t="s">
+        <v>97</v>
       </c>
     </row>
-    <row r="4" ht="24" customHeight="1" spans="1:69" x14ac:dyDescent="0.25">
+    <row r="4" ht="24" customHeight="1" spans="1:70" x14ac:dyDescent="0.25">
       <c r="A4" s="13">
         <v>3</v>
       </c>
@@ -2268,84 +3067,106 @@
         <v>70</v>
       </c>
       <c r="C4" s="14" t="s">
-        <v>80</v>
+        <v>118</v>
       </c>
       <c r="D4" s="14" t="s">
-        <v>70</v>
+        <v>119</v>
       </c>
       <c r="E4" s="14" t="s">
-        <v>70</v>
+        <v>120</v>
+      </c>
+      <c r="F4" s="14" t="s">
+        <v>74</v>
       </c>
       <c r="G4" s="14" t="s">
-        <v>72</v>
+        <v>121</v>
       </c>
       <c r="H4" s="14" t="s">
+        <v>122</v>
+      </c>
+      <c r="I4" s="14" t="s">
+        <v>123</v>
+      </c>
+      <c r="J4" s="14" t="s">
+        <v>124</v>
+      </c>
+      <c r="K4" s="14" t="s">
+        <v>125</v>
+      </c>
+      <c r="L4" s="14" t="s">
+        <v>126</v>
+      </c>
+      <c r="M4" s="14" t="s">
         <v>81</v>
       </c>
-      <c r="I4" s="14" t="s">
-        <v>70</v>
-      </c>
-      <c r="J4" s="14" t="s">
+      <c r="N4" s="14" t="s">
         <v>82</v>
       </c>
-      <c r="K4" s="14" t="s">
+      <c r="O4" s="15">
+        <v>6061</v>
+      </c>
+      <c r="P4" s="15">
+        <v>-5349</v>
+      </c>
+      <c r="Q4" s="16">
+        <v>-13.51</v>
+      </c>
+      <c r="R4" s="17" t="s">
         <v>83</v>
       </c>
-      <c r="L4" s="14" t="s">
-        <v>80</v>
-      </c>
-      <c r="M4" s="1"/>
-      <c r="N4" s="14" t="s">
-        <v>70</v>
-      </c>
-      <c r="O4" s="15" t="s">
-        <v>70</v>
-      </c>
-      <c r="P4" s="15" t="s">
-        <v>70</v>
-      </c>
-      <c r="Q4" s="16" t="s">
-        <v>70</v>
-      </c>
-      <c r="R4" s="17" t="s">
-        <v>70</v>
-      </c>
       <c r="S4" s="18" t="s">
-        <v>70</v>
-      </c>
-      <c r="T4" s="15" t="s">
-        <v>70</v>
-      </c>
-      <c r="U4" s="16" t="s">
-        <v>70</v>
-      </c>
-      <c r="V4" s="15" t="s">
-        <v>70</v>
+        <v>127</v>
+      </c>
+      <c r="T4" s="15">
+        <v>1841</v>
+      </c>
+      <c r="U4" s="16">
+        <v>0.58</v>
+      </c>
+      <c r="V4" s="15">
+        <v>403179</v>
       </c>
       <c r="W4" s="15" t="s">
-        <v>70</v>
-      </c>
-      <c r="X4" s="15" t="s">
-        <v>70</v>
-      </c>
-      <c r="Z4" s="23">
-        <v>209.69</v>
-      </c>
+        <v>85</v>
+      </c>
+      <c r="X4" s="15">
+        <v>231520</v>
+      </c>
+      <c r="Y4" s="19">
+        <v>5</v>
+      </c>
+      <c r="Z4" s="20">
+        <v>209.55</v>
+      </c>
+      <c r="AA4" s="4"/>
+      <c r="AB4" s="1"/>
+      <c r="AC4" s="2"/>
       <c r="AD4" s="19">
         <v>1634</v>
       </c>
-      <c r="AF4" s="20">
+      <c r="AE4" s="15">
+        <v>914</v>
+      </c>
+      <c r="AF4" s="21">
         <v>4.2</v>
       </c>
-      <c r="AG4" s="21">
-        <v>0</v>
+      <c r="AG4" s="22">
+        <v>0.4965</v>
+      </c>
+      <c r="AH4" s="20">
+        <v>7.5</v>
       </c>
       <c r="AI4" s="16">
-        <v>0</v>
-      </c>
-      <c r="AK4" s="1"/>
-      <c r="AL4" s="19" t="s">
-        <v>70</v>
+        <v>0.82</v>
+      </c>
+      <c r="AK4" s="13" t="s">
+        <v>128</v>
+      </c>
+      <c r="AL4" s="19">
+        <v>578</v>
+      </c>
+      <c r="AM4" s="13" t="s">
+        <v>129</v>
       </c>
       <c r="AN4" s="13" t="s">
         <v>70</v>
@@ -2353,8 +3174,20 @@
       <c r="AO4" s="13" t="s">
         <v>70</v>
       </c>
-      <c r="AQ4" s="19" t="s">
-        <v>70</v>
+      <c r="AP4" s="20">
+        <v>130.46</v>
+      </c>
+      <c r="AQ4" s="19">
+        <v>10</v>
+      </c>
+      <c r="AR4" s="19">
+        <v>1</v>
+      </c>
+      <c r="AS4" s="14" t="s">
+        <v>88</v>
+      </c>
+      <c r="AT4" s="13" t="s">
+        <v>129</v>
       </c>
       <c r="AU4" s="13" t="s">
         <v>70</v>
@@ -2369,7 +3202,7 @@
         <v>70</v>
       </c>
       <c r="AY4" s="13" t="s">
-        <v>70</v>
+        <v>89</v>
       </c>
       <c r="AZ4" s="13" t="s">
         <v>70</v>
@@ -2381,16 +3214,16 @@
         <v>70</v>
       </c>
       <c r="BC4" s="13" t="s">
-        <v>70</v>
+        <v>89</v>
       </c>
       <c r="BD4" s="13" t="s">
-        <v>70</v>
+        <v>89</v>
       </c>
       <c r="BE4" s="13" t="s">
         <v>70</v>
       </c>
       <c r="BF4" s="13" t="s">
-        <v>70</v>
+        <v>89</v>
       </c>
       <c r="BG4" s="13" t="s">
         <v>70</v>
@@ -2398,20 +3231,38 @@
       <c r="BH4" s="14" t="s">
         <v>70</v>
       </c>
-      <c r="BK4" s="22" t="s">
-        <v>70</v>
-      </c>
-      <c r="BM4" s="22" t="s">
-        <v>70</v>
-      </c>
-      <c r="BO4" s="22" t="s">
-        <v>70</v>
-      </c>
-      <c r="BQ4" s="22" t="s">
-        <v>70</v>
+      <c r="BI4" s="23" t="s">
+        <v>90</v>
+      </c>
+      <c r="BJ4" s="23" t="s">
+        <v>130</v>
+      </c>
+      <c r="BK4" s="23" t="s">
+        <v>131</v>
+      </c>
+      <c r="BL4" s="23" t="s">
+        <v>132</v>
+      </c>
+      <c r="BM4" s="23" t="s">
+        <v>133</v>
+      </c>
+      <c r="BN4" s="23" t="s">
+        <v>134</v>
+      </c>
+      <c r="BO4" s="23" t="s">
+        <v>134</v>
+      </c>
+      <c r="BP4" s="23" t="s">
+        <v>135</v>
+      </c>
+      <c r="BQ4" s="23" t="s">
+        <v>136</v>
+      </c>
+      <c r="BR4" s="13" t="s">
+        <v>97</v>
       </c>
     </row>
-    <row r="5" ht="24" customHeight="1" spans="1:69" x14ac:dyDescent="0.25">
+    <row r="5" ht="24" customHeight="1" spans="1:70" x14ac:dyDescent="0.25">
       <c r="A5" s="13">
         <v>4</v>
       </c>
@@ -2419,106 +3270,142 @@
         <v>70</v>
       </c>
       <c r="C5" s="14" t="s">
-        <v>84</v>
+        <v>137</v>
       </c>
       <c r="D5" s="14" t="s">
-        <v>70</v>
+        <v>138</v>
       </c>
       <c r="E5" s="14" t="s">
-        <v>70</v>
+        <v>139</v>
+      </c>
+      <c r="F5" s="14" t="s">
+        <v>140</v>
       </c>
       <c r="G5" s="14" t="s">
-        <v>72</v>
+        <v>141</v>
       </c>
       <c r="H5" s="14" t="s">
-        <v>85</v>
+        <v>142</v>
       </c>
       <c r="I5" s="14" t="s">
-        <v>70</v>
+        <v>143</v>
       </c>
       <c r="J5" s="14" t="s">
-        <v>86</v>
+        <v>144</v>
       </c>
       <c r="K5" s="14" t="s">
+        <v>145</v>
+      </c>
+      <c r="L5" s="14" t="s">
+        <v>146</v>
+      </c>
+      <c r="M5" s="14" t="s">
+        <v>81</v>
+      </c>
+      <c r="N5" s="14" t="s">
+        <v>82</v>
+      </c>
+      <c r="O5" s="15">
+        <v>38624</v>
+      </c>
+      <c r="P5" s="15">
+        <v>-20674</v>
+      </c>
+      <c r="Q5" s="16">
+        <v>-0.64</v>
+      </c>
+      <c r="R5" s="17" t="s">
+        <v>83</v>
+      </c>
+      <c r="S5" s="18" t="s">
+        <v>147</v>
+      </c>
+      <c r="T5" s="15">
+        <v>191</v>
+      </c>
+      <c r="U5" s="16">
+        <v>0.14</v>
+      </c>
+      <c r="V5" s="15">
+        <v>95309</v>
+      </c>
+      <c r="W5" s="15" t="s">
+        <v>148</v>
+      </c>
+      <c r="X5" s="15">
+        <v>23933</v>
+      </c>
+      <c r="Y5" s="19">
+        <v>3</v>
+      </c>
+      <c r="Z5" s="20">
+        <v>499</v>
+      </c>
+      <c r="AA5" s="4"/>
+      <c r="AB5" s="1"/>
+      <c r="AC5" s="15">
+        <v>11</v>
+      </c>
+      <c r="AD5" s="19">
+        <v>1673</v>
+      </c>
+      <c r="AE5" s="15">
+        <v>93</v>
+      </c>
+      <c r="AF5" s="21">
+        <v>4.2</v>
+      </c>
+      <c r="AG5" s="22">
+        <v>0.4869</v>
+      </c>
+      <c r="AH5" s="20">
+        <v>7.31</v>
+      </c>
+      <c r="AI5" s="16">
+        <v>0.84</v>
+      </c>
+      <c r="AK5" s="13" t="s">
+        <v>149</v>
+      </c>
+      <c r="AL5" s="19">
+        <v>641</v>
+      </c>
+      <c r="AM5" s="13" t="s">
         <v>87</v>
       </c>
-      <c r="L5" s="14" t="s">
-        <v>84</v>
-      </c>
-      <c r="M5" s="1"/>
-      <c r="N5" s="14" t="s">
-        <v>70</v>
-      </c>
-      <c r="O5" s="15" t="s">
-        <v>70</v>
-      </c>
-      <c r="P5" s="15" t="s">
-        <v>70</v>
-      </c>
-      <c r="Q5" s="16" t="s">
-        <v>70</v>
-      </c>
-      <c r="R5" s="17" t="s">
-        <v>70</v>
-      </c>
-      <c r="S5" s="18" t="s">
-        <v>70</v>
-      </c>
-      <c r="T5" s="15" t="s">
-        <v>70</v>
-      </c>
-      <c r="U5" s="16" t="s">
-        <v>70</v>
-      </c>
-      <c r="V5" s="15" t="s">
-        <v>70</v>
-      </c>
-      <c r="W5" s="15" t="s">
-        <v>70</v>
-      </c>
-      <c r="X5" s="15" t="s">
-        <v>70</v>
-      </c>
-      <c r="Z5" s="4"/>
-      <c r="AD5" s="19">
-        <v>1672</v>
-      </c>
-      <c r="AF5" s="20">
-        <v>4.2</v>
-      </c>
-      <c r="AG5" s="21">
-        <v>0</v>
-      </c>
-      <c r="AI5" s="16">
-        <v>0</v>
-      </c>
-      <c r="AK5" s="1"/>
-      <c r="AL5" s="19" t="s">
-        <v>70</v>
-      </c>
       <c r="AN5" s="13" t="s">
         <v>70</v>
       </c>
       <c r="AO5" s="13" t="s">
         <v>70</v>
       </c>
-      <c r="AQ5" s="19" t="s">
-        <v>70</v>
+      <c r="AP5" s="4"/>
+      <c r="AQ5" s="19">
+        <v>10</v>
+      </c>
+      <c r="AR5" s="19">
+        <v>2</v>
+      </c>
+      <c r="AS5" s="14" t="s">
+        <v>140</v>
+      </c>
+      <c r="AT5" s="13" t="s">
+        <v>87</v>
       </c>
       <c r="AU5" s="13" t="s">
-        <v>70</v>
+        <v>150</v>
       </c>
       <c r="AV5" s="14" t="s">
-        <v>70</v>
+        <v>151</v>
       </c>
       <c r="AW5" s="13" t="s">
-        <v>70</v>
+        <v>152</v>
       </c>
       <c r="AX5" s="13" t="s">
         <v>70</v>
       </c>
       <c r="AY5" s="13" t="s">
-        <v>70</v>
+        <v>89</v>
       </c>
       <c r="AZ5" s="13" t="s">
         <v>70</v>
@@ -2530,16 +3417,16 @@
         <v>70</v>
       </c>
       <c r="BC5" s="13" t="s">
-        <v>70</v>
+        <v>89</v>
       </c>
       <c r="BD5" s="13" t="s">
-        <v>70</v>
+        <v>89</v>
       </c>
       <c r="BE5" s="13" t="s">
         <v>70</v>
       </c>
       <c r="BF5" s="13" t="s">
-        <v>70</v>
+        <v>89</v>
       </c>
       <c r="BG5" s="13" t="s">
         <v>70</v>
@@ -2547,20 +3434,38 @@
       <c r="BH5" s="14" t="s">
         <v>70</v>
       </c>
-      <c r="BK5" s="22" t="s">
-        <v>70</v>
-      </c>
-      <c r="BM5" s="22" t="s">
-        <v>70</v>
-      </c>
-      <c r="BO5" s="22" t="s">
-        <v>70</v>
-      </c>
-      <c r="BQ5" s="22" t="s">
-        <v>70</v>
+      <c r="BI5" s="23" t="s">
+        <v>90</v>
+      </c>
+      <c r="BJ5" s="23" t="s">
+        <v>153</v>
+      </c>
+      <c r="BK5" s="23" t="s">
+        <v>154</v>
+      </c>
+      <c r="BL5" s="23" t="s">
+        <v>155</v>
+      </c>
+      <c r="BM5" s="23" t="s">
+        <v>156</v>
+      </c>
+      <c r="BN5" s="23" t="s">
+        <v>157</v>
+      </c>
+      <c r="BO5" s="23" t="s">
+        <v>158</v>
+      </c>
+      <c r="BP5" s="23" t="s">
+        <v>159</v>
+      </c>
+      <c r="BQ5" s="23" t="s">
+        <v>160</v>
+      </c>
+      <c r="BR5" s="13" t="s">
+        <v>97</v>
       </c>
     </row>
-    <row r="6" ht="24" customHeight="1" spans="1:69" x14ac:dyDescent="0.25">
+    <row r="6" ht="24" customHeight="1" spans="1:70" x14ac:dyDescent="0.25">
       <c r="A6" s="13">
         <v>5</v>
       </c>
@@ -2568,148 +3473,200 @@
         <v>70</v>
       </c>
       <c r="C6" s="14" t="s">
-        <v>88</v>
+        <v>161</v>
       </c>
       <c r="D6" s="14" t="s">
-        <v>70</v>
+        <v>162</v>
       </c>
       <c r="E6" s="14" t="s">
-        <v>70</v>
+        <v>163</v>
+      </c>
+      <c r="F6" s="14" t="s">
+        <v>140</v>
       </c>
       <c r="G6" s="14" t="s">
-        <v>72</v>
+        <v>164</v>
       </c>
       <c r="H6" s="14" t="s">
+        <v>165</v>
+      </c>
+      <c r="I6" s="14" t="s">
+        <v>166</v>
+      </c>
+      <c r="J6" s="14" t="s">
+        <v>167</v>
+      </c>
+      <c r="K6" s="14" t="s">
+        <v>168</v>
+      </c>
+      <c r="L6" s="14" t="s">
+        <v>169</v>
+      </c>
+      <c r="M6" s="14" t="s">
+        <v>81</v>
+      </c>
+      <c r="N6" s="14" t="s">
+        <v>82</v>
+      </c>
+      <c r="O6" s="15">
+        <v>21329</v>
+      </c>
+      <c r="P6" s="15">
+        <v>36605</v>
+      </c>
+      <c r="Q6" s="16">
+        <v>0.58</v>
+      </c>
+      <c r="R6" s="17" t="s">
+        <v>83</v>
+      </c>
+      <c r="S6" s="18" t="s">
+        <v>170</v>
+      </c>
+      <c r="T6" s="15">
+        <v>183</v>
+      </c>
+      <c r="U6" s="16">
+        <v>0.47</v>
+      </c>
+      <c r="V6" s="15">
+        <v>137067</v>
+      </c>
+      <c r="W6" s="15" t="s">
+        <v>148</v>
+      </c>
+      <c r="X6" s="15">
+        <v>37122</v>
+      </c>
+      <c r="Y6" s="19">
+        <v>3</v>
+      </c>
+      <c r="Z6" s="20">
+        <v>749</v>
+      </c>
+      <c r="AA6" s="4"/>
+      <c r="AB6" s="1"/>
+      <c r="AC6" s="2"/>
+      <c r="AD6" s="19">
+        <v>448</v>
+      </c>
+      <c r="AE6" s="15">
+        <v>55</v>
+      </c>
+      <c r="AF6" s="21">
+        <v>4.3</v>
+      </c>
+      <c r="AG6" s="22">
+        <v>0.3005</v>
+      </c>
+      <c r="AH6" s="20">
+        <v>7.03</v>
+      </c>
+      <c r="AI6" s="16">
+        <v>0.84</v>
+      </c>
+      <c r="AK6" s="13" t="s">
+        <v>171</v>
+      </c>
+      <c r="AL6" s="19">
+        <v>341</v>
+      </c>
+      <c r="AM6" s="13" t="s">
+        <v>87</v>
+      </c>
+      <c r="AN6" s="13" t="s">
+        <v>70</v>
+      </c>
+      <c r="AO6" s="13" t="s">
+        <v>70</v>
+      </c>
+      <c r="AP6" s="4"/>
+      <c r="AQ6" s="19">
+        <v>10</v>
+      </c>
+      <c r="AR6" s="19">
+        <v>1</v>
+      </c>
+      <c r="AS6" s="14" t="s">
+        <v>140</v>
+      </c>
+      <c r="AT6" s="13" t="s">
+        <v>87</v>
+      </c>
+      <c r="AU6" s="13" t="s">
+        <v>150</v>
+      </c>
+      <c r="AV6" s="14" t="s">
+        <v>151</v>
+      </c>
+      <c r="AW6" s="13" t="s">
+        <v>152</v>
+      </c>
+      <c r="AX6" s="13" t="s">
+        <v>70</v>
+      </c>
+      <c r="AY6" s="13" t="s">
         <v>89</v>
       </c>
-      <c r="I6" s="14" t="s">
-        <v>70</v>
-      </c>
-      <c r="J6" s="14" t="s">
+      <c r="AZ6" s="13" t="s">
+        <v>70</v>
+      </c>
+      <c r="BA6" s="13" t="s">
+        <v>70</v>
+      </c>
+      <c r="BB6" s="13" t="s">
+        <v>70</v>
+      </c>
+      <c r="BC6" s="13" t="s">
+        <v>89</v>
+      </c>
+      <c r="BD6" s="13" t="s">
+        <v>89</v>
+      </c>
+      <c r="BE6" s="13" t="s">
+        <v>70</v>
+      </c>
+      <c r="BF6" s="13" t="s">
+        <v>89</v>
+      </c>
+      <c r="BG6" s="13" t="s">
+        <v>70</v>
+      </c>
+      <c r="BH6" s="14" t="s">
+        <v>70</v>
+      </c>
+      <c r="BI6" s="23" t="s">
         <v>90</v>
       </c>
-      <c r="K6" s="14" t="s">
-        <v>91</v>
-      </c>
-      <c r="L6" s="14" t="s">
-        <v>88</v>
-      </c>
-      <c r="M6" s="1"/>
-      <c r="N6" s="14" t="s">
-        <v>70</v>
-      </c>
-      <c r="O6" s="15" t="s">
-        <v>70</v>
-      </c>
-      <c r="P6" s="15" t="s">
-        <v>70</v>
-      </c>
-      <c r="Q6" s="16" t="s">
-        <v>70</v>
-      </c>
-      <c r="R6" s="17" t="s">
-        <v>70</v>
-      </c>
-      <c r="S6" s="18" t="s">
-        <v>70</v>
-      </c>
-      <c r="T6" s="15" t="s">
-        <v>70</v>
-      </c>
-      <c r="U6" s="16" t="s">
-        <v>70</v>
-      </c>
-      <c r="V6" s="15" t="s">
-        <v>70</v>
-      </c>
-      <c r="W6" s="15" t="s">
-        <v>70</v>
-      </c>
-      <c r="X6" s="15" t="s">
-        <v>70</v>
-      </c>
-      <c r="Z6" s="4"/>
-      <c r="AD6" s="19">
-        <v>447</v>
-      </c>
-      <c r="AF6" s="20">
-        <v>4.3</v>
-      </c>
-      <c r="AG6" s="21">
-        <v>0</v>
-      </c>
-      <c r="AI6" s="16">
-        <v>0</v>
-      </c>
-      <c r="AK6" s="1"/>
-      <c r="AL6" s="19" t="s">
-        <v>70</v>
-      </c>
-      <c r="AN6" s="13" t="s">
-        <v>70</v>
-      </c>
-      <c r="AO6" s="13" t="s">
-        <v>70</v>
-      </c>
-      <c r="AQ6" s="19" t="s">
-        <v>70</v>
-      </c>
-      <c r="AU6" s="13" t="s">
-        <v>70</v>
-      </c>
-      <c r="AV6" s="14" t="s">
-        <v>70</v>
-      </c>
-      <c r="AW6" s="13" t="s">
-        <v>70</v>
-      </c>
-      <c r="AX6" s="13" t="s">
-        <v>70</v>
-      </c>
-      <c r="AY6" s="13" t="s">
-        <v>70</v>
-      </c>
-      <c r="AZ6" s="13" t="s">
-        <v>70</v>
-      </c>
-      <c r="BA6" s="13" t="s">
-        <v>70</v>
-      </c>
-      <c r="BB6" s="13" t="s">
-        <v>70</v>
-      </c>
-      <c r="BC6" s="13" t="s">
-        <v>70</v>
-      </c>
-      <c r="BD6" s="13" t="s">
-        <v>70</v>
-      </c>
-      <c r="BE6" s="13" t="s">
-        <v>70</v>
-      </c>
-      <c r="BF6" s="13" t="s">
-        <v>70</v>
-      </c>
-      <c r="BG6" s="13" t="s">
-        <v>70</v>
-      </c>
-      <c r="BH6" s="14" t="s">
-        <v>70</v>
-      </c>
-      <c r="BK6" s="22" t="s">
-        <v>70</v>
-      </c>
-      <c r="BM6" s="22" t="s">
-        <v>70</v>
-      </c>
-      <c r="BO6" s="22" t="s">
-        <v>70</v>
-      </c>
-      <c r="BQ6" s="22" t="s">
-        <v>70</v>
+      <c r="BJ6" s="23" t="s">
+        <v>172</v>
+      </c>
+      <c r="BK6" s="23" t="s">
+        <v>173</v>
+      </c>
+      <c r="BL6" s="23" t="s">
+        <v>174</v>
+      </c>
+      <c r="BM6" s="23" t="s">
+        <v>175</v>
+      </c>
+      <c r="BN6" s="23" t="s">
+        <v>176</v>
+      </c>
+      <c r="BO6" s="23" t="s">
+        <v>173</v>
+      </c>
+      <c r="BP6" s="23" t="s">
+        <v>177</v>
+      </c>
+      <c r="BQ6" s="23" t="s">
+        <v>178</v>
+      </c>
+      <c r="BR6" s="13" t="s">
+        <v>97</v>
       </c>
     </row>
-    <row r="7" ht="24" customHeight="1" spans="1:69" x14ac:dyDescent="0.25">
+    <row r="7" ht="24" customHeight="1" spans="1:70" x14ac:dyDescent="0.25">
       <c r="A7" s="13">
         <v>6</v>
       </c>
@@ -2717,50 +3674,52 @@
         <v>70</v>
       </c>
       <c r="C7" s="14" t="s">
-        <v>92</v>
+        <v>179</v>
       </c>
       <c r="D7" s="14" t="s">
         <v>70</v>
       </c>
       <c r="E7" s="14" t="s">
-        <v>70</v>
+        <v>180</v>
+      </c>
+      <c r="F7" s="14" t="s">
+        <v>181</v>
       </c>
       <c r="G7" s="14" t="s">
-        <v>72</v>
+        <v>182</v>
       </c>
       <c r="H7" s="14" t="s">
-        <v>93</v>
+        <v>183</v>
       </c>
       <c r="I7" s="14" t="s">
-        <v>70</v>
+        <v>184</v>
       </c>
       <c r="J7" s="14" t="s">
-        <v>94</v>
+        <v>185</v>
       </c>
       <c r="K7" s="14" t="s">
-        <v>95</v>
+        <v>186</v>
       </c>
       <c r="L7" s="14" t="s">
-        <v>92</v>
-      </c>
-      <c r="M7" s="1"/>
+        <v>179</v>
+      </c>
+      <c r="M7" s="14" t="s">
+        <v>81</v>
+      </c>
       <c r="N7" s="14" t="s">
-        <v>70</v>
-      </c>
-      <c r="O7" s="15" t="s">
-        <v>70</v>
-      </c>
-      <c r="P7" s="15" t="s">
-        <v>70</v>
-      </c>
-      <c r="Q7" s="16" t="s">
-        <v>70</v>
+        <v>82</v>
+      </c>
+      <c r="O7" s="15">
+        <v>97417</v>
+      </c>
+      <c r="Q7" s="16">
+        <v>0</v>
       </c>
       <c r="R7" s="17" t="s">
-        <v>70</v>
+        <v>83</v>
       </c>
       <c r="S7" s="18" t="s">
-        <v>70</v>
+        <v>187</v>
       </c>
       <c r="T7" s="15" t="s">
         <v>70</v>
@@ -2777,14 +3736,20 @@
       <c r="X7" s="15" t="s">
         <v>70</v>
       </c>
+      <c r="Y7" s="19">
+        <v>1</v>
+      </c>
       <c r="Z7" s="4"/>
+      <c r="AA7" s="4"/>
+      <c r="AB7" s="1"/>
+      <c r="AC7" s="2"/>
       <c r="AD7" s="19">
         <v>5</v>
       </c>
-      <c r="AF7" s="20">
+      <c r="AF7" s="21">
         <v>5</v>
       </c>
-      <c r="AG7" s="21">
+      <c r="AG7" s="22">
         <v>0</v>
       </c>
       <c r="AI7" s="16">
@@ -2794,15 +3759,24 @@
       <c r="AL7" s="19" t="s">
         <v>70</v>
       </c>
+      <c r="AM7" s="13" t="s">
+        <v>87</v>
+      </c>
       <c r="AN7" s="13" t="s">
         <v>70</v>
       </c>
       <c r="AO7" s="13" t="s">
         <v>70</v>
       </c>
+      <c r="AP7" s="4"/>
       <c r="AQ7" s="19" t="s">
         <v>70</v>
       </c>
+      <c r="AR7" s="2"/>
+      <c r="AS7" s="1"/>
+      <c r="AT7" s="13" t="s">
+        <v>87</v>
+      </c>
       <c r="AU7" s="13" t="s">
         <v>70</v>
       </c>
@@ -2828,7 +3802,7 @@
         <v>70</v>
       </c>
       <c r="BC7" s="13" t="s">
-        <v>70</v>
+        <v>89</v>
       </c>
       <c r="BD7" s="13" t="s">
         <v>70</v>
@@ -2845,20 +3819,27 @@
       <c r="BH7" s="14" t="s">
         <v>70</v>
       </c>
-      <c r="BK7" s="22" t="s">
-        <v>70</v>
-      </c>
-      <c r="BM7" s="22" t="s">
-        <v>70</v>
-      </c>
-      <c r="BO7" s="22" t="s">
-        <v>70</v>
-      </c>
-      <c r="BQ7" s="22" t="s">
-        <v>70</v>
-      </c>
+      <c r="BJ7" s="23" t="s">
+        <v>188</v>
+      </c>
+      <c r="BK7" s="23" t="s">
+        <v>189</v>
+      </c>
+      <c r="BL7" s="1"/>
+      <c r="BM7" s="23" t="s">
+        <v>70</v>
+      </c>
+      <c r="BN7" s="1"/>
+      <c r="BO7" s="23" t="s">
+        <v>70</v>
+      </c>
+      <c r="BP7" s="1"/>
+      <c r="BQ7" s="23" t="s">
+        <v>70</v>
+      </c>
+      <c r="BR7" s="1"/>
     </row>
-    <row r="8" ht="24" customHeight="1" spans="1:69" x14ac:dyDescent="0.25">
+    <row r="8" ht="24" customHeight="1" spans="1:70" x14ac:dyDescent="0.25">
       <c r="A8" s="13">
         <v>7</v>
       </c>
@@ -2866,150 +3847,202 @@
         <v>70</v>
       </c>
       <c r="C8" s="14" t="s">
-        <v>96</v>
+        <v>190</v>
       </c>
       <c r="D8" s="14" t="s">
         <v>70</v>
       </c>
       <c r="E8" s="14" t="s">
-        <v>70</v>
+        <v>191</v>
+      </c>
+      <c r="F8" s="14" t="s">
+        <v>192</v>
       </c>
       <c r="G8" s="14" t="s">
-        <v>72</v>
+        <v>193</v>
       </c>
       <c r="H8" s="14" t="s">
+        <v>194</v>
+      </c>
+      <c r="I8" s="14" t="s">
+        <v>195</v>
+      </c>
+      <c r="J8" s="14" t="s">
+        <v>196</v>
+      </c>
+      <c r="K8" s="14" t="s">
+        <v>197</v>
+      </c>
+      <c r="L8" s="14" t="s">
+        <v>190</v>
+      </c>
+      <c r="M8" s="14" t="s">
+        <v>81</v>
+      </c>
+      <c r="N8" s="14" t="s">
+        <v>82</v>
+      </c>
+      <c r="O8" s="15">
+        <v>327824</v>
+      </c>
+      <c r="P8" s="15">
+        <v>-56981</v>
+      </c>
+      <c r="Q8" s="16">
+        <v>-0.07</v>
+      </c>
+      <c r="R8" s="17" t="s">
+        <v>83</v>
+      </c>
+      <c r="S8" s="18" t="s">
+        <v>198</v>
+      </c>
+      <c r="T8" s="15">
+        <v>2</v>
+      </c>
+      <c r="U8" s="16">
+        <v>-0.76</v>
+      </c>
+      <c r="V8" s="15">
+        <v>1158</v>
+      </c>
+      <c r="W8" s="15" t="s">
+        <v>70</v>
+      </c>
+      <c r="X8" s="15" t="s">
+        <v>70</v>
+      </c>
+      <c r="Y8" s="19">
+        <v>1</v>
+      </c>
+      <c r="Z8" s="20">
+        <v>430.58</v>
+      </c>
+      <c r="AA8" s="4"/>
+      <c r="AB8" s="1"/>
+      <c r="AC8" s="2"/>
+      <c r="AD8" s="19">
+        <v>52</v>
+      </c>
+      <c r="AE8" s="15">
+        <v>6</v>
+      </c>
+      <c r="AF8" s="21">
+        <v>4.3</v>
+      </c>
+      <c r="AG8" s="22">
+        <v>0</v>
+      </c>
+      <c r="AH8" s="20">
+        <v>8.04</v>
+      </c>
+      <c r="AI8" s="16">
+        <v>0.84</v>
+      </c>
+      <c r="AK8" s="13" t="s">
+        <v>199</v>
+      </c>
+      <c r="AL8" s="19">
+        <v>402</v>
+      </c>
+      <c r="AM8" s="13" t="s">
+        <v>129</v>
+      </c>
+      <c r="AN8" s="13" t="s">
+        <v>70</v>
+      </c>
+      <c r="AO8" s="13" t="s">
+        <v>70</v>
+      </c>
+      <c r="AP8" s="20">
+        <v>153.6</v>
+      </c>
+      <c r="AQ8" s="19">
+        <v>10</v>
+      </c>
+      <c r="AR8" s="19">
+        <v>1</v>
+      </c>
+      <c r="AS8" s="14" t="s">
+        <v>88</v>
+      </c>
+      <c r="AT8" s="13" t="s">
+        <v>129</v>
+      </c>
+      <c r="AU8" s="13" t="s">
+        <v>70</v>
+      </c>
+      <c r="AV8" s="14" t="s">
+        <v>70</v>
+      </c>
+      <c r="AW8" s="13" t="s">
+        <v>70</v>
+      </c>
+      <c r="AX8" s="13" t="s">
+        <v>70</v>
+      </c>
+      <c r="AY8" s="13" t="s">
+        <v>89</v>
+      </c>
+      <c r="AZ8" s="13" t="s">
+        <v>70</v>
+      </c>
+      <c r="BA8" s="13" t="s">
+        <v>70</v>
+      </c>
+      <c r="BB8" s="13" t="s">
+        <v>70</v>
+      </c>
+      <c r="BC8" s="13" t="s">
+        <v>89</v>
+      </c>
+      <c r="BD8" s="13" t="s">
+        <v>89</v>
+      </c>
+      <c r="BE8" s="13" t="s">
+        <v>70</v>
+      </c>
+      <c r="BF8" s="13" t="s">
+        <v>89</v>
+      </c>
+      <c r="BG8" s="13" t="s">
+        <v>70</v>
+      </c>
+      <c r="BH8" s="14" t="s">
+        <v>70</v>
+      </c>
+      <c r="BI8" s="23" t="s">
+        <v>90</v>
+      </c>
+      <c r="BJ8" s="23" t="s">
+        <v>200</v>
+      </c>
+      <c r="BK8" s="23" t="s">
+        <v>201</v>
+      </c>
+      <c r="BL8" s="23" t="s">
+        <v>202</v>
+      </c>
+      <c r="BM8" s="23" t="s">
+        <v>203</v>
+      </c>
+      <c r="BN8" s="23" t="s">
+        <v>204</v>
+      </c>
+      <c r="BO8" s="23" t="s">
+        <v>204</v>
+      </c>
+      <c r="BP8" s="23" t="s">
+        <v>205</v>
+      </c>
+      <c r="BQ8" s="23" t="s">
+        <v>206</v>
+      </c>
+      <c r="BR8" s="13" t="s">
         <v>97</v>
       </c>
-      <c r="I8" s="14" t="s">
-        <v>70</v>
-      </c>
-      <c r="J8" s="14" t="s">
-        <v>98</v>
-      </c>
-      <c r="K8" s="14" t="s">
-        <v>99</v>
-      </c>
-      <c r="L8" s="14" t="s">
-        <v>96</v>
-      </c>
-      <c r="M8" s="1"/>
-      <c r="N8" s="14" t="s">
-        <v>70</v>
-      </c>
-      <c r="O8" s="15" t="s">
-        <v>70</v>
-      </c>
-      <c r="P8" s="15" t="s">
-        <v>70</v>
-      </c>
-      <c r="Q8" s="16" t="s">
-        <v>70</v>
-      </c>
-      <c r="R8" s="17" t="s">
-        <v>70</v>
-      </c>
-      <c r="S8" s="18" t="s">
-        <v>70</v>
-      </c>
-      <c r="T8" s="15" t="s">
-        <v>70</v>
-      </c>
-      <c r="U8" s="16" t="s">
-        <v>70</v>
-      </c>
-      <c r="V8" s="15" t="s">
-        <v>70</v>
-      </c>
-      <c r="W8" s="15" t="s">
-        <v>70</v>
-      </c>
-      <c r="X8" s="15" t="s">
-        <v>70</v>
-      </c>
-      <c r="Z8" s="23">
-        <v>430.87</v>
-      </c>
-      <c r="AD8" s="19">
-        <v>51</v>
-      </c>
-      <c r="AF8" s="20">
-        <v>4.3</v>
-      </c>
-      <c r="AG8" s="21">
-        <v>0</v>
-      </c>
-      <c r="AI8" s="16">
-        <v>0</v>
-      </c>
-      <c r="AK8" s="1"/>
-      <c r="AL8" s="19" t="s">
-        <v>70</v>
-      </c>
-      <c r="AN8" s="13" t="s">
-        <v>70</v>
-      </c>
-      <c r="AO8" s="13" t="s">
-        <v>70</v>
-      </c>
-      <c r="AQ8" s="19" t="s">
-        <v>70</v>
-      </c>
-      <c r="AU8" s="13" t="s">
-        <v>70</v>
-      </c>
-      <c r="AV8" s="14" t="s">
-        <v>70</v>
-      </c>
-      <c r="AW8" s="13" t="s">
-        <v>70</v>
-      </c>
-      <c r="AX8" s="13" t="s">
-        <v>70</v>
-      </c>
-      <c r="AY8" s="13" t="s">
-        <v>70</v>
-      </c>
-      <c r="AZ8" s="13" t="s">
-        <v>70</v>
-      </c>
-      <c r="BA8" s="13" t="s">
-        <v>70</v>
-      </c>
-      <c r="BB8" s="13" t="s">
-        <v>70</v>
-      </c>
-      <c r="BC8" s="13" t="s">
-        <v>70</v>
-      </c>
-      <c r="BD8" s="13" t="s">
-        <v>70</v>
-      </c>
-      <c r="BE8" s="13" t="s">
-        <v>70</v>
-      </c>
-      <c r="BF8" s="13" t="s">
-        <v>70</v>
-      </c>
-      <c r="BG8" s="13" t="s">
-        <v>70</v>
-      </c>
-      <c r="BH8" s="14" t="s">
-        <v>70</v>
-      </c>
-      <c r="BK8" s="22" t="s">
-        <v>70</v>
-      </c>
-      <c r="BM8" s="22" t="s">
-        <v>70</v>
-      </c>
-      <c r="BO8" s="22" t="s">
-        <v>70</v>
-      </c>
-      <c r="BQ8" s="22" t="s">
-        <v>70</v>
-      </c>
     </row>
-    <row r="9" ht="24" customHeight="1" spans="1:69" x14ac:dyDescent="0.25">
+    <row r="9" ht="24" customHeight="1" spans="1:70" x14ac:dyDescent="0.25">
       <c r="A9" s="13">
         <v>8</v>
       </c>
@@ -3017,59 +4050,64 @@
         <v>70</v>
       </c>
       <c r="C9" s="14" t="s">
-        <v>100</v>
+        <v>207</v>
       </c>
       <c r="D9" s="14" t="s">
-        <v>70</v>
+        <v>208</v>
       </c>
       <c r="E9" s="14" t="s">
-        <v>70</v>
+        <v>209</v>
+      </c>
+      <c r="F9" s="14" t="s">
+        <v>101</v>
       </c>
       <c r="G9" s="14" t="s">
-        <v>72</v>
+        <v>210</v>
       </c>
       <c r="H9" s="14" t="s">
-        <v>101</v>
+        <v>211</v>
       </c>
       <c r="I9" s="14" t="s">
-        <v>70</v>
+        <v>212</v>
       </c>
       <c r="J9" s="14" t="s">
-        <v>102</v>
+        <v>213</v>
       </c>
       <c r="K9" s="14" t="s">
-        <v>103</v>
+        <v>214</v>
       </c>
       <c r="L9" s="14" t="s">
-        <v>100</v>
-      </c>
-      <c r="M9" s="1"/>
+        <v>215</v>
+      </c>
+      <c r="M9" s="14" t="s">
+        <v>81</v>
+      </c>
       <c r="N9" s="14" t="s">
-        <v>70</v>
-      </c>
-      <c r="O9" s="15" t="s">
-        <v>70</v>
-      </c>
-      <c r="P9" s="15" t="s">
-        <v>70</v>
-      </c>
-      <c r="Q9" s="16" t="s">
-        <v>70</v>
+        <v>82</v>
+      </c>
+      <c r="O9" s="15">
+        <v>364039</v>
+      </c>
+      <c r="P9" s="15">
+        <v>369524</v>
+      </c>
+      <c r="Q9" s="16">
+        <v>0.76</v>
       </c>
       <c r="R9" s="17" t="s">
-        <v>70</v>
+        <v>83</v>
       </c>
       <c r="S9" s="18" t="s">
-        <v>70</v>
-      </c>
-      <c r="T9" s="15" t="s">
-        <v>70</v>
-      </c>
-      <c r="U9" s="16" t="s">
-        <v>70</v>
-      </c>
-      <c r="V9" s="15" t="s">
-        <v>70</v>
+        <v>216</v>
+      </c>
+      <c r="T9" s="15">
+        <v>9</v>
+      </c>
+      <c r="U9" s="16">
+        <v>-0.73</v>
+      </c>
+      <c r="V9" s="15">
+        <v>4050</v>
       </c>
       <c r="W9" s="15" t="s">
         <v>70</v>
@@ -3077,24 +4115,41 @@
       <c r="X9" s="15" t="s">
         <v>70</v>
       </c>
-      <c r="Z9" s="23">
-        <v>430.87</v>
-      </c>
+      <c r="Y9" s="19">
+        <v>1</v>
+      </c>
+      <c r="Z9" s="20">
+        <v>430.58</v>
+      </c>
+      <c r="AA9" s="4"/>
+      <c r="AB9" s="1"/>
+      <c r="AC9" s="2"/>
       <c r="AD9" s="19">
         <v>130</v>
       </c>
-      <c r="AF9" s="20">
+      <c r="AE9" s="15">
+        <v>10</v>
+      </c>
+      <c r="AF9" s="21">
         <v>4.1</v>
       </c>
-      <c r="AG9" s="21">
+      <c r="AG9" s="22">
         <v>0</v>
       </c>
+      <c r="AH9" s="20">
+        <v>7.13</v>
+      </c>
       <c r="AI9" s="16">
-        <v>0</v>
-      </c>
-      <c r="AK9" s="1"/>
-      <c r="AL9" s="19" t="s">
-        <v>70</v>
+        <v>0.83</v>
+      </c>
+      <c r="AK9" s="13" t="s">
+        <v>217</v>
+      </c>
+      <c r="AL9" s="19">
+        <v>370</v>
+      </c>
+      <c r="AM9" s="13" t="s">
+        <v>129</v>
       </c>
       <c r="AN9" s="13" t="s">
         <v>70</v>
@@ -3102,8 +4157,20 @@
       <c r="AO9" s="13" t="s">
         <v>70</v>
       </c>
-      <c r="AQ9" s="19" t="s">
-        <v>70</v>
+      <c r="AP9" s="20">
+        <v>103.82</v>
+      </c>
+      <c r="AQ9" s="19">
+        <v>10</v>
+      </c>
+      <c r="AR9" s="19">
+        <v>1</v>
+      </c>
+      <c r="AS9" s="14" t="s">
+        <v>88</v>
+      </c>
+      <c r="AT9" s="13" t="s">
+        <v>129</v>
       </c>
       <c r="AU9" s="13" t="s">
         <v>70</v>
@@ -3130,16 +4197,16 @@
         <v>70</v>
       </c>
       <c r="BC9" s="13" t="s">
-        <v>70</v>
+        <v>89</v>
       </c>
       <c r="BD9" s="13" t="s">
-        <v>70</v>
+        <v>89</v>
       </c>
       <c r="BE9" s="13" t="s">
         <v>70</v>
       </c>
       <c r="BF9" s="13" t="s">
-        <v>70</v>
+        <v>89</v>
       </c>
       <c r="BG9" s="13" t="s">
         <v>70</v>
@@ -3147,20 +4214,35 @@
       <c r="BH9" s="14" t="s">
         <v>70</v>
       </c>
-      <c r="BK9" s="22" t="s">
-        <v>70</v>
-      </c>
-      <c r="BM9" s="22" t="s">
-        <v>70</v>
-      </c>
-      <c r="BO9" s="22" t="s">
-        <v>70</v>
-      </c>
-      <c r="BQ9" s="22" t="s">
-        <v>70</v>
+      <c r="BJ9" s="23" t="s">
+        <v>218</v>
+      </c>
+      <c r="BK9" s="23" t="s">
+        <v>219</v>
+      </c>
+      <c r="BL9" s="23" t="s">
+        <v>220</v>
+      </c>
+      <c r="BM9" s="23" t="s">
+        <v>221</v>
+      </c>
+      <c r="BN9" s="23" t="s">
+        <v>222</v>
+      </c>
+      <c r="BO9" s="23" t="s">
+        <v>222</v>
+      </c>
+      <c r="BP9" s="23" t="s">
+        <v>223</v>
+      </c>
+      <c r="BQ9" s="23" t="s">
+        <v>224</v>
+      </c>
+      <c r="BR9" s="13" t="s">
+        <v>97</v>
       </c>
     </row>
-    <row r="10" ht="24" customHeight="1" spans="1:69" x14ac:dyDescent="0.25">
+    <row r="10" ht="24" customHeight="1" spans="1:70" x14ac:dyDescent="0.25">
       <c r="A10" s="13">
         <v>9</v>
       </c>
@@ -3168,59 +4250,64 @@
         <v>70</v>
       </c>
       <c r="C10" s="14" t="s">
-        <v>104</v>
+        <v>225</v>
       </c>
       <c r="D10" s="14" t="s">
-        <v>70</v>
+        <v>226</v>
       </c>
       <c r="E10" s="14" t="s">
-        <v>70</v>
+        <v>227</v>
+      </c>
+      <c r="F10" s="14" t="s">
+        <v>101</v>
       </c>
       <c r="G10" s="14" t="s">
-        <v>72</v>
+        <v>228</v>
       </c>
       <c r="H10" s="14" t="s">
-        <v>105</v>
+        <v>229</v>
       </c>
       <c r="I10" s="14" t="s">
-        <v>70</v>
+        <v>230</v>
       </c>
       <c r="J10" s="14" t="s">
-        <v>106</v>
+        <v>231</v>
       </c>
       <c r="K10" s="14" t="s">
-        <v>107</v>
+        <v>232</v>
       </c>
       <c r="L10" s="14" t="s">
-        <v>104</v>
-      </c>
-      <c r="M10" s="1"/>
+        <v>233</v>
+      </c>
+      <c r="M10" s="14" t="s">
+        <v>81</v>
+      </c>
       <c r="N10" s="14" t="s">
-        <v>70</v>
-      </c>
-      <c r="O10" s="15" t="s">
-        <v>70</v>
-      </c>
-      <c r="P10" s="15" t="s">
-        <v>70</v>
-      </c>
-      <c r="Q10" s="16" t="s">
-        <v>70</v>
+        <v>82</v>
+      </c>
+      <c r="O10" s="15">
+        <v>392677</v>
+      </c>
+      <c r="P10" s="15">
+        <v>-759</v>
+      </c>
+      <c r="Q10" s="16">
+        <v>-0.12</v>
       </c>
       <c r="R10" s="17" t="s">
-        <v>70</v>
+        <v>83</v>
       </c>
       <c r="S10" s="18" t="s">
-        <v>70</v>
-      </c>
-      <c r="T10" s="15" t="s">
-        <v>70</v>
-      </c>
-      <c r="U10" s="16" t="s">
-        <v>70</v>
-      </c>
-      <c r="V10" s="15" t="s">
-        <v>70</v>
+        <v>234</v>
+      </c>
+      <c r="T10" s="15">
+        <v>868</v>
+      </c>
+      <c r="U10" s="16">
+        <v>0.22</v>
+      </c>
+      <c r="V10" s="15">
+        <v>137083</v>
       </c>
       <c r="W10" s="15" t="s">
         <v>70</v>
@@ -3228,24 +4315,41 @@
       <c r="X10" s="15" t="s">
         <v>70</v>
       </c>
-      <c r="Z10" s="23">
-        <v>70.9</v>
-      </c>
+      <c r="Y10" s="19">
+        <v>1</v>
+      </c>
+      <c r="Z10" s="20">
+        <v>157.93</v>
+      </c>
+      <c r="AA10" s="4"/>
+      <c r="AB10" s="1"/>
+      <c r="AC10" s="2"/>
       <c r="AD10" s="19">
-        <v>17</v>
-      </c>
-      <c r="AF10" s="20">
-        <v>4.2</v>
-      </c>
-      <c r="AG10" s="21">
-        <v>0</v>
+        <v>824</v>
+      </c>
+      <c r="AE10" s="15">
+        <v>161</v>
+      </c>
+      <c r="AF10" s="21">
+        <v>4.1</v>
+      </c>
+      <c r="AG10" s="22">
+        <v>0.1855</v>
+      </c>
+      <c r="AH10" s="20">
+        <v>7.31</v>
       </c>
       <c r="AI10" s="16">
-        <v>0</v>
-      </c>
-      <c r="AK10" s="1"/>
-      <c r="AL10" s="19" t="s">
-        <v>70</v>
+        <v>0.81</v>
+      </c>
+      <c r="AK10" s="13" t="s">
+        <v>235</v>
+      </c>
+      <c r="AL10" s="19">
+        <v>711</v>
+      </c>
+      <c r="AM10" s="13" t="s">
+        <v>87</v>
       </c>
       <c r="AN10" s="13" t="s">
         <v>70</v>
@@ -3253,8 +4357,18 @@
       <c r="AO10" s="13" t="s">
         <v>70</v>
       </c>
-      <c r="AQ10" s="19" t="s">
-        <v>70</v>
+      <c r="AP10" s="4"/>
+      <c r="AQ10" s="19">
+        <v>10</v>
+      </c>
+      <c r="AR10" s="19">
+        <v>5</v>
+      </c>
+      <c r="AS10" s="14" t="s">
+        <v>88</v>
+      </c>
+      <c r="AT10" s="13" t="s">
+        <v>87</v>
       </c>
       <c r="AU10" s="13" t="s">
         <v>70</v>
@@ -3269,7 +4383,7 @@
         <v>70</v>
       </c>
       <c r="AY10" s="13" t="s">
-        <v>70</v>
+        <v>89</v>
       </c>
       <c r="AZ10" s="13" t="s">
         <v>70</v>
@@ -3281,16 +4395,16 @@
         <v>70</v>
       </c>
       <c r="BC10" s="13" t="s">
-        <v>70</v>
+        <v>89</v>
       </c>
       <c r="BD10" s="13" t="s">
-        <v>70</v>
+        <v>89</v>
       </c>
       <c r="BE10" s="13" t="s">
         <v>70</v>
       </c>
       <c r="BF10" s="13" t="s">
-        <v>70</v>
+        <v>89</v>
       </c>
       <c r="BG10" s="13" t="s">
         <v>70</v>
@@ -3298,20 +4412,38 @@
       <c r="BH10" s="14" t="s">
         <v>70</v>
       </c>
-      <c r="BK10" s="22" t="s">
-        <v>70</v>
-      </c>
-      <c r="BM10" s="22" t="s">
-        <v>70</v>
-      </c>
-      <c r="BO10" s="22" t="s">
-        <v>70</v>
-      </c>
-      <c r="BQ10" s="22" t="s">
-        <v>70</v>
+      <c r="BI10" s="23" t="s">
+        <v>90</v>
+      </c>
+      <c r="BJ10" s="23" t="s">
+        <v>236</v>
+      </c>
+      <c r="BK10" s="23" t="s">
+        <v>237</v>
+      </c>
+      <c r="BL10" s="23" t="s">
+        <v>238</v>
+      </c>
+      <c r="BM10" s="23" t="s">
+        <v>70</v>
+      </c>
+      <c r="BN10" s="23" t="s">
+        <v>239</v>
+      </c>
+      <c r="BO10" s="23" t="s">
+        <v>239</v>
+      </c>
+      <c r="BP10" s="23" t="s">
+        <v>240</v>
+      </c>
+      <c r="BQ10" s="23" t="s">
+        <v>241</v>
+      </c>
+      <c r="BR10" s="13" t="s">
+        <v>97</v>
       </c>
     </row>
-    <row r="11" ht="24" customHeight="1" spans="1:69" x14ac:dyDescent="0.25">
+    <row r="11" ht="24" customHeight="1" spans="1:70" x14ac:dyDescent="0.25">
       <c r="A11" s="13">
         <v>10</v>
       </c>
@@ -3319,59 +4451,64 @@
         <v>70</v>
       </c>
       <c r="C11" s="14" t="s">
-        <v>108</v>
+        <v>242</v>
       </c>
       <c r="D11" s="14" t="s">
-        <v>70</v>
+        <v>243</v>
       </c>
       <c r="E11" s="14" t="s">
-        <v>70</v>
+        <v>244</v>
+      </c>
+      <c r="F11" s="14" t="s">
+        <v>245</v>
       </c>
       <c r="G11" s="14" t="s">
-        <v>72</v>
+        <v>246</v>
       </c>
       <c r="H11" s="14" t="s">
-        <v>109</v>
+        <v>247</v>
       </c>
       <c r="I11" s="14" t="s">
-        <v>70</v>
+        <v>248</v>
       </c>
       <c r="J11" s="14" t="s">
-        <v>110</v>
+        <v>249</v>
       </c>
       <c r="K11" s="14" t="s">
-        <v>111</v>
+        <v>250</v>
       </c>
       <c r="L11" s="14" t="s">
-        <v>108</v>
-      </c>
-      <c r="M11" s="1"/>
+        <v>251</v>
+      </c>
+      <c r="M11" s="14" t="s">
+        <v>81</v>
+      </c>
       <c r="N11" s="14" t="s">
-        <v>70</v>
-      </c>
-      <c r="O11" s="15" t="s">
-        <v>70</v>
-      </c>
-      <c r="P11" s="15" t="s">
-        <v>70</v>
-      </c>
-      <c r="Q11" s="16" t="s">
-        <v>70</v>
+        <v>82</v>
+      </c>
+      <c r="O11" s="15">
+        <v>436476</v>
+      </c>
+      <c r="P11" s="15">
+        <v>796</v>
+      </c>
+      <c r="Q11" s="16">
+        <v>0.06</v>
       </c>
       <c r="R11" s="17" t="s">
-        <v>70</v>
+        <v>83</v>
       </c>
       <c r="S11" s="18" t="s">
-        <v>70</v>
-      </c>
-      <c r="T11" s="15" t="s">
-        <v>70</v>
-      </c>
-      <c r="U11" s="16" t="s">
-        <v>70</v>
-      </c>
-      <c r="V11" s="15" t="s">
-        <v>70</v>
+        <v>252</v>
+      </c>
+      <c r="T11" s="15">
+        <v>269</v>
+      </c>
+      <c r="U11" s="16">
+        <v>0.87</v>
+      </c>
+      <c r="V11" s="15">
+        <v>19917</v>
       </c>
       <c r="W11" s="15" t="s">
         <v>70</v>
@@ -3379,22 +4516,41 @@
       <c r="X11" s="15" t="s">
         <v>70</v>
       </c>
-      <c r="Z11" s="4"/>
+      <c r="Y11" s="19">
+        <v>4</v>
+      </c>
+      <c r="Z11" s="20">
+        <v>70.85</v>
+      </c>
+      <c r="AA11" s="4"/>
+      <c r="AB11" s="1"/>
+      <c r="AC11" s="2"/>
       <c r="AD11" s="19">
-        <v>823</v>
-      </c>
-      <c r="AF11" s="20">
-        <v>4.1</v>
-      </c>
-      <c r="AG11" s="21">
-        <v>0</v>
+        <v>17</v>
+      </c>
+      <c r="AE11" s="15">
+        <v>8</v>
+      </c>
+      <c r="AF11" s="21">
+        <v>4.2</v>
+      </c>
+      <c r="AG11" s="22">
+        <v>0.0297</v>
+      </c>
+      <c r="AH11" s="20">
+        <v>7.4</v>
       </c>
       <c r="AI11" s="16">
-        <v>0</v>
-      </c>
-      <c r="AK11" s="1"/>
-      <c r="AL11" s="19" t="s">
-        <v>70</v>
+        <v>0.75</v>
+      </c>
+      <c r="AK11" s="13" t="s">
+        <v>253</v>
+      </c>
+      <c r="AL11" s="19">
+        <v>250</v>
+      </c>
+      <c r="AM11" s="13" t="s">
+        <v>129</v>
       </c>
       <c r="AN11" s="13" t="s">
         <v>70</v>
@@ -3402,8 +4558,20 @@
       <c r="AO11" s="13" t="s">
         <v>70</v>
       </c>
-      <c r="AQ11" s="19" t="s">
-        <v>70</v>
+      <c r="AP11" s="20">
+        <v>115.76</v>
+      </c>
+      <c r="AQ11" s="19">
+        <v>8</v>
+      </c>
+      <c r="AR11" s="19">
+        <v>1</v>
+      </c>
+      <c r="AS11" s="14" t="s">
+        <v>88</v>
+      </c>
+      <c r="AT11" s="13" t="s">
+        <v>129</v>
       </c>
       <c r="AU11" s="13" t="s">
         <v>70</v>
@@ -3418,7 +4586,7 @@
         <v>70</v>
       </c>
       <c r="AY11" s="13" t="s">
-        <v>70</v>
+        <v>89</v>
       </c>
       <c r="AZ11" s="13" t="s">
         <v>70</v>
@@ -3430,7 +4598,7 @@
         <v>70</v>
       </c>
       <c r="BC11" s="13" t="s">
-        <v>70</v>
+        <v>89</v>
       </c>
       <c r="BD11" s="13" t="s">
         <v>70</v>
@@ -3447,20 +4615,36 @@
       <c r="BH11" s="14" t="s">
         <v>70</v>
       </c>
-      <c r="BK11" s="22" t="s">
-        <v>70</v>
-      </c>
-      <c r="BM11" s="22" t="s">
-        <v>70</v>
-      </c>
-      <c r="BO11" s="22" t="s">
-        <v>70</v>
-      </c>
-      <c r="BQ11" s="22" t="s">
-        <v>70</v>
+      <c r="BI11" s="23" t="s">
+        <v>90</v>
+      </c>
+      <c r="BJ11" s="23" t="s">
+        <v>254</v>
+      </c>
+      <c r="BK11" s="23" t="s">
+        <v>255</v>
+      </c>
+      <c r="BL11" s="1"/>
+      <c r="BM11" s="23" t="s">
+        <v>70</v>
+      </c>
+      <c r="BN11" s="23" t="s">
+        <v>255</v>
+      </c>
+      <c r="BO11" s="23" t="s">
+        <v>255</v>
+      </c>
+      <c r="BP11" s="23" t="s">
+        <v>256</v>
+      </c>
+      <c r="BQ11" s="23" t="s">
+        <v>257</v>
+      </c>
+      <c r="BR11" s="13" t="s">
+        <v>97</v>
       </c>
     </row>
-    <row r="12" ht="24" customHeight="1" spans="1:69" x14ac:dyDescent="0.25">
+    <row r="12" ht="24" customHeight="1" spans="1:70" x14ac:dyDescent="0.25">
       <c r="A12" s="13">
         <v>11</v>
       </c>
@@ -3468,56 +4652,61 @@
         <v>70</v>
       </c>
       <c r="C12" s="14" t="s">
-        <v>112</v>
+        <v>258</v>
       </c>
       <c r="D12" s="14" t="s">
         <v>70</v>
       </c>
       <c r="E12" s="14" t="s">
-        <v>70</v>
+        <v>259</v>
+      </c>
+      <c r="F12" s="14" t="s">
+        <v>260</v>
       </c>
       <c r="G12" s="14" t="s">
-        <v>72</v>
+        <v>261</v>
       </c>
       <c r="H12" s="14" t="s">
-        <v>113</v>
+        <v>262</v>
       </c>
       <c r="I12" s="14" t="s">
-        <v>70</v>
+        <v>263</v>
       </c>
       <c r="J12" s="14" t="s">
-        <v>114</v>
+        <v>264</v>
       </c>
       <c r="K12" s="14" t="s">
-        <v>115</v>
+        <v>265</v>
       </c>
       <c r="L12" s="14" t="s">
-        <v>112</v>
-      </c>
-      <c r="M12" s="1"/>
+        <v>258</v>
+      </c>
+      <c r="M12" s="14" t="s">
+        <v>81</v>
+      </c>
       <c r="N12" s="14" t="s">
-        <v>70</v>
-      </c>
-      <c r="O12" s="15" t="s">
-        <v>70</v>
-      </c>
-      <c r="P12" s="15" t="s">
-        <v>70</v>
-      </c>
-      <c r="Q12" s="16" t="s">
-        <v>70</v>
+        <v>82</v>
+      </c>
+      <c r="O12" s="15">
+        <v>668289</v>
+      </c>
+      <c r="P12" s="15">
+        <v>-7604</v>
+      </c>
+      <c r="Q12" s="16">
+        <v>-0.01</v>
       </c>
       <c r="R12" s="17" t="s">
-        <v>70</v>
+        <v>83</v>
       </c>
       <c r="S12" s="18" t="s">
-        <v>70</v>
+        <v>266</v>
       </c>
       <c r="T12" s="15" t="s">
         <v>70</v>
       </c>
-      <c r="U12" s="16" t="s">
-        <v>70</v>
+      <c r="U12" s="16">
+        <v>-0.97</v>
       </c>
       <c r="V12" s="15" t="s">
         <v>70</v>
@@ -3528,22 +4717,41 @@
       <c r="X12" s="15" t="s">
         <v>70</v>
       </c>
-      <c r="Z12" s="4"/>
+      <c r="Y12" s="19">
+        <v>1</v>
+      </c>
+      <c r="Z12" s="20">
+        <v>319.99</v>
+      </c>
+      <c r="AA12" s="4"/>
+      <c r="AB12" s="1"/>
+      <c r="AC12" s="2"/>
       <c r="AD12" s="19">
         <v>39</v>
       </c>
-      <c r="AF12" s="20">
+      <c r="AE12" s="15">
+        <v>0</v>
+      </c>
+      <c r="AF12" s="21">
         <v>3.3</v>
       </c>
-      <c r="AG12" s="21">
+      <c r="AG12" s="22">
         <v>0</v>
       </c>
+      <c r="AH12" s="20">
+        <v>7.31</v>
+      </c>
       <c r="AI12" s="16">
-        <v>0</v>
-      </c>
-      <c r="AK12" s="1"/>
-      <c r="AL12" s="19" t="s">
-        <v>70</v>
+        <v>0.83</v>
+      </c>
+      <c r="AK12" s="13" t="s">
+        <v>267</v>
+      </c>
+      <c r="AL12" s="19">
+        <v>208</v>
+      </c>
+      <c r="AM12" s="13" t="s">
+        <v>87</v>
       </c>
       <c r="AN12" s="13" t="s">
         <v>70</v>
@@ -3551,17 +4759,27 @@
       <c r="AO12" s="13" t="s">
         <v>70</v>
       </c>
-      <c r="AQ12" s="19" t="s">
-        <v>70</v>
+      <c r="AP12" s="4"/>
+      <c r="AQ12" s="19">
+        <v>8</v>
+      </c>
+      <c r="AR12" s="19">
+        <v>1</v>
+      </c>
+      <c r="AS12" s="14" t="s">
+        <v>268</v>
+      </c>
+      <c r="AT12" s="13" t="s">
+        <v>87</v>
       </c>
       <c r="AU12" s="13" t="s">
-        <v>70</v>
+        <v>269</v>
       </c>
       <c r="AV12" s="14" t="s">
-        <v>70</v>
+        <v>270</v>
       </c>
       <c r="AW12" s="13" t="s">
-        <v>70</v>
+        <v>271</v>
       </c>
       <c r="AX12" s="13" t="s">
         <v>70</v>
@@ -3579,16 +4797,16 @@
         <v>70</v>
       </c>
       <c r="BC12" s="13" t="s">
-        <v>70</v>
+        <v>89</v>
       </c>
       <c r="BD12" s="13" t="s">
-        <v>70</v>
+        <v>89</v>
       </c>
       <c r="BE12" s="13" t="s">
         <v>70</v>
       </c>
       <c r="BF12" s="13" t="s">
-        <v>70</v>
+        <v>89</v>
       </c>
       <c r="BG12" s="13" t="s">
         <v>70</v>
@@ -3596,20 +4814,35 @@
       <c r="BH12" s="14" t="s">
         <v>70</v>
       </c>
-      <c r="BK12" s="22" t="s">
-        <v>70</v>
-      </c>
-      <c r="BM12" s="22" t="s">
-        <v>70</v>
-      </c>
-      <c r="BO12" s="22" t="s">
-        <v>70</v>
-      </c>
-      <c r="BQ12" s="22" t="s">
-        <v>70</v>
+      <c r="BJ12" s="23" t="s">
+        <v>272</v>
+      </c>
+      <c r="BK12" s="23" t="s">
+        <v>70</v>
+      </c>
+      <c r="BL12" s="23" t="s">
+        <v>273</v>
+      </c>
+      <c r="BM12" s="23" t="s">
+        <v>274</v>
+      </c>
+      <c r="BN12" s="23" t="s">
+        <v>275</v>
+      </c>
+      <c r="BO12" s="23" t="s">
+        <v>275</v>
+      </c>
+      <c r="BP12" s="23" t="s">
+        <v>276</v>
+      </c>
+      <c r="BQ12" s="23" t="s">
+        <v>277</v>
+      </c>
+      <c r="BR12" s="13" t="s">
+        <v>97</v>
       </c>
     </row>
-    <row r="13" ht="24" customHeight="1" spans="1:69" x14ac:dyDescent="0.25">
+    <row r="13" ht="24" customHeight="1" spans="1:70" x14ac:dyDescent="0.25">
       <c r="A13" s="13">
         <v>12</v>
       </c>
@@ -3617,59 +4850,64 @@
         <v>70</v>
       </c>
       <c r="C13" s="14" t="s">
-        <v>116</v>
+        <v>278</v>
       </c>
       <c r="D13" s="14" t="s">
         <v>70</v>
       </c>
       <c r="E13" s="14" t="s">
-        <v>70</v>
+        <v>279</v>
+      </c>
+      <c r="F13" s="14" t="s">
+        <v>192</v>
       </c>
       <c r="G13" s="14" t="s">
-        <v>72</v>
+        <v>280</v>
       </c>
       <c r="H13" s="14" t="s">
-        <v>117</v>
+        <v>281</v>
       </c>
       <c r="I13" s="14" t="s">
-        <v>70</v>
+        <v>282</v>
       </c>
       <c r="J13" s="14" t="s">
-        <v>118</v>
+        <v>283</v>
       </c>
       <c r="K13" s="14" t="s">
-        <v>119</v>
+        <v>284</v>
       </c>
       <c r="L13" s="14" t="s">
-        <v>116</v>
-      </c>
-      <c r="M13" s="1"/>
+        <v>278</v>
+      </c>
+      <c r="M13" s="14" t="s">
+        <v>81</v>
+      </c>
       <c r="N13" s="14" t="s">
-        <v>70</v>
-      </c>
-      <c r="O13" s="15" t="s">
-        <v>70</v>
-      </c>
-      <c r="P13" s="15" t="s">
-        <v>70</v>
-      </c>
-      <c r="Q13" s="16" t="s">
-        <v>70</v>
+        <v>82</v>
+      </c>
+      <c r="O13" s="15">
+        <v>686659</v>
+      </c>
+      <c r="P13" s="15">
+        <v>-59830</v>
+      </c>
+      <c r="Q13" s="16">
+        <v>-0.1</v>
       </c>
       <c r="R13" s="17" t="s">
-        <v>70</v>
+        <v>83</v>
       </c>
       <c r="S13" s="18" t="s">
-        <v>70</v>
-      </c>
-      <c r="T13" s="15" t="s">
-        <v>70</v>
-      </c>
-      <c r="U13" s="16" t="s">
-        <v>70</v>
-      </c>
-      <c r="V13" s="15" t="s">
-        <v>70</v>
+        <v>285</v>
+      </c>
+      <c r="T13" s="15">
+        <v>12</v>
+      </c>
+      <c r="U13" s="16">
+        <v>-0.42</v>
+      </c>
+      <c r="V13" s="15">
+        <v>2040</v>
       </c>
       <c r="W13" s="15" t="s">
         <v>70</v>
@@ -3677,18 +4915,41 @@
       <c r="X13" s="15" t="s">
         <v>70</v>
       </c>
-      <c r="Z13" s="4"/>
-      <c r="AD13" s="2"/>
-      <c r="AF13" s="5"/>
-      <c r="AG13" s="21">
+      <c r="Y13" s="19">
+        <v>1</v>
+      </c>
+      <c r="Z13" s="20">
+        <v>162.66</v>
+      </c>
+      <c r="AA13" s="4"/>
+      <c r="AB13" s="1"/>
+      <c r="AC13" s="2"/>
+      <c r="AD13" s="19">
+        <v>109</v>
+      </c>
+      <c r="AE13" s="15">
         <v>0</v>
       </c>
+      <c r="AF13" s="21">
+        <v>4.1</v>
+      </c>
+      <c r="AG13" s="22">
+        <v>0</v>
+      </c>
+      <c r="AH13" s="20">
+        <v>7.13</v>
+      </c>
       <c r="AI13" s="16">
-        <v>0</v>
-      </c>
-      <c r="AK13" s="1"/>
-      <c r="AL13" s="19" t="s">
-        <v>70</v>
+        <v>0.81</v>
+      </c>
+      <c r="AK13" s="13" t="s">
+        <v>286</v>
+      </c>
+      <c r="AL13" s="19">
+        <v>382</v>
+      </c>
+      <c r="AM13" s="13" t="s">
+        <v>129</v>
       </c>
       <c r="AN13" s="13" t="s">
         <v>70</v>
@@ -3696,8 +4957,20 @@
       <c r="AO13" s="13" t="s">
         <v>70</v>
       </c>
-      <c r="AQ13" s="19" t="s">
-        <v>70</v>
+      <c r="AP13" s="20">
+        <v>115.67</v>
+      </c>
+      <c r="AQ13" s="19">
+        <v>10</v>
+      </c>
+      <c r="AR13" s="19">
+        <v>1</v>
+      </c>
+      <c r="AS13" s="14" t="s">
+        <v>88</v>
+      </c>
+      <c r="AT13" s="13" t="s">
+        <v>129</v>
       </c>
       <c r="AU13" s="13" t="s">
         <v>70</v>
@@ -3712,7 +4985,7 @@
         <v>70</v>
       </c>
       <c r="AY13" s="13" t="s">
-        <v>70</v>
+        <v>89</v>
       </c>
       <c r="AZ13" s="13" t="s">
         <v>70</v>
@@ -3724,16 +4997,16 @@
         <v>70</v>
       </c>
       <c r="BC13" s="13" t="s">
-        <v>70</v>
+        <v>89</v>
       </c>
       <c r="BD13" s="13" t="s">
-        <v>70</v>
+        <v>89</v>
       </c>
       <c r="BE13" s="13" t="s">
         <v>70</v>
       </c>
       <c r="BF13" s="13" t="s">
-        <v>70</v>
+        <v>89</v>
       </c>
       <c r="BG13" s="13" t="s">
         <v>70</v>
@@ -3741,20 +5014,38 @@
       <c r="BH13" s="14" t="s">
         <v>70</v>
       </c>
-      <c r="BK13" s="22" t="s">
-        <v>70</v>
-      </c>
-      <c r="BM13" s="22" t="s">
-        <v>70</v>
-      </c>
-      <c r="BO13" s="22" t="s">
-        <v>70</v>
-      </c>
-      <c r="BQ13" s="22" t="s">
-        <v>70</v>
+      <c r="BI13" s="23" t="s">
+        <v>90</v>
+      </c>
+      <c r="BJ13" s="23" t="s">
+        <v>287</v>
+      </c>
+      <c r="BK13" s="23" t="s">
+        <v>288</v>
+      </c>
+      <c r="BL13" s="23" t="s">
+        <v>289</v>
+      </c>
+      <c r="BM13" s="23" t="s">
+        <v>290</v>
+      </c>
+      <c r="BN13" s="23" t="s">
+        <v>291</v>
+      </c>
+      <c r="BO13" s="23" t="s">
+        <v>291</v>
+      </c>
+      <c r="BP13" s="23" t="s">
+        <v>292</v>
+      </c>
+      <c r="BQ13" s="23" t="s">
+        <v>293</v>
+      </c>
+      <c r="BR13" s="13" t="s">
+        <v>97</v>
       </c>
     </row>
-    <row r="14" ht="24" customHeight="1" spans="1:69" x14ac:dyDescent="0.25">
+    <row r="14" ht="24" customHeight="1" spans="1:70" x14ac:dyDescent="0.25">
       <c r="A14" s="13">
         <v>13</v>
       </c>
@@ -3762,59 +5053,64 @@
         <v>70</v>
       </c>
       <c r="C14" s="14" t="s">
-        <v>120</v>
+        <v>294</v>
       </c>
       <c r="D14" s="14" t="s">
         <v>70</v>
       </c>
       <c r="E14" s="14" t="s">
-        <v>70</v>
+        <v>295</v>
+      </c>
+      <c r="F14" s="14" t="s">
+        <v>296</v>
       </c>
       <c r="G14" s="14" t="s">
-        <v>72</v>
+        <v>297</v>
       </c>
       <c r="H14" s="14" t="s">
-        <v>121</v>
+        <v>298</v>
       </c>
       <c r="I14" s="14" t="s">
-        <v>70</v>
+        <v>299</v>
       </c>
       <c r="J14" s="14" t="s">
-        <v>122</v>
+        <v>300</v>
       </c>
       <c r="K14" s="14" t="s">
-        <v>123</v>
+        <v>301</v>
       </c>
       <c r="L14" s="14" t="s">
-        <v>120</v>
-      </c>
-      <c r="M14" s="1"/>
+        <v>294</v>
+      </c>
+      <c r="M14" s="14" t="s">
+        <v>81</v>
+      </c>
       <c r="N14" s="14" t="s">
-        <v>70</v>
-      </c>
-      <c r="O14" s="15" t="s">
-        <v>70</v>
-      </c>
-      <c r="P14" s="15" t="s">
-        <v>70</v>
-      </c>
-      <c r="Q14" s="16" t="s">
-        <v>70</v>
+        <v>82</v>
+      </c>
+      <c r="O14" s="15">
+        <v>698016</v>
+      </c>
+      <c r="P14" s="15">
+        <v>34966</v>
+      </c>
+      <c r="Q14" s="16">
+        <v>0.1</v>
       </c>
       <c r="R14" s="17" t="s">
-        <v>70</v>
+        <v>83</v>
       </c>
       <c r="S14" s="18" t="s">
-        <v>70</v>
-      </c>
-      <c r="T14" s="15" t="s">
-        <v>70</v>
+        <v>302</v>
+      </c>
+      <c r="T14" s="15">
+        <v>8</v>
       </c>
       <c r="U14" s="16" t="s">
         <v>70</v>
       </c>
-      <c r="V14" s="15" t="s">
-        <v>70</v>
+      <c r="V14" s="15">
+        <v>816</v>
       </c>
       <c r="W14" s="15" t="s">
         <v>70</v>
@@ -3822,24 +5118,35 @@
       <c r="X14" s="15" t="s">
         <v>70</v>
       </c>
-      <c r="Z14" s="23">
-        <v>162.77</v>
-      </c>
-      <c r="AD14" s="19">
-        <v>109</v>
-      </c>
-      <c r="AF14" s="20">
-        <v>4.1</v>
-      </c>
-      <c r="AG14" s="21">
+      <c r="Y14" s="19">
+        <v>1</v>
+      </c>
+      <c r="Z14" s="20">
+        <v>101.99</v>
+      </c>
+      <c r="AA14" s="4"/>
+      <c r="AB14" s="1"/>
+      <c r="AC14" s="2"/>
+      <c r="AD14" s="2"/>
+      <c r="AE14" s="2"/>
+      <c r="AF14" s="5"/>
+      <c r="AG14" s="22">
         <v>0</v>
       </c>
+      <c r="AH14" s="20">
+        <v>5.29</v>
+      </c>
       <c r="AI14" s="16">
-        <v>0</v>
-      </c>
-      <c r="AK14" s="1"/>
-      <c r="AL14" s="19" t="s">
-        <v>70</v>
+        <v>0.8</v>
+      </c>
+      <c r="AK14" s="13" t="s">
+        <v>303</v>
+      </c>
+      <c r="AL14" s="19">
+        <v>41</v>
+      </c>
+      <c r="AM14" s="13" t="s">
+        <v>87</v>
       </c>
       <c r="AN14" s="13" t="s">
         <v>70</v>
@@ -3847,17 +5154,27 @@
       <c r="AO14" s="13" t="s">
         <v>70</v>
       </c>
-      <c r="AQ14" s="19" t="s">
-        <v>70</v>
+      <c r="AP14" s="4"/>
+      <c r="AQ14" s="19">
+        <v>6</v>
+      </c>
+      <c r="AR14" s="19">
+        <v>1</v>
+      </c>
+      <c r="AS14" s="14" t="s">
+        <v>296</v>
+      </c>
+      <c r="AT14" s="13" t="s">
+        <v>87</v>
       </c>
       <c r="AU14" s="13" t="s">
-        <v>70</v>
+        <v>269</v>
       </c>
       <c r="AV14" s="14" t="s">
-        <v>70</v>
+        <v>304</v>
       </c>
       <c r="AW14" s="13" t="s">
-        <v>70</v>
+        <v>305</v>
       </c>
       <c r="AX14" s="13" t="s">
         <v>70</v>
@@ -3892,20 +5209,35 @@
       <c r="BH14" s="14" t="s">
         <v>70</v>
       </c>
-      <c r="BK14" s="22" t="s">
-        <v>70</v>
-      </c>
-      <c r="BM14" s="22" t="s">
-        <v>70</v>
-      </c>
-      <c r="BO14" s="22" t="s">
-        <v>70</v>
-      </c>
-      <c r="BQ14" s="22" t="s">
-        <v>70</v>
+      <c r="BJ14" s="23" t="s">
+        <v>306</v>
+      </c>
+      <c r="BK14" s="23" t="s">
+        <v>307</v>
+      </c>
+      <c r="BL14" s="23" t="s">
+        <v>308</v>
+      </c>
+      <c r="BM14" s="23" t="s">
+        <v>309</v>
+      </c>
+      <c r="BN14" s="23" t="s">
+        <v>310</v>
+      </c>
+      <c r="BO14" s="23" t="s">
+        <v>189</v>
+      </c>
+      <c r="BP14" s="23" t="s">
+        <v>311</v>
+      </c>
+      <c r="BQ14" s="23" t="s">
+        <v>312</v>
+      </c>
+      <c r="BR14" s="13" t="s">
+        <v>313</v>
       </c>
     </row>
-    <row r="15" ht="24" customHeight="1" spans="1:69" x14ac:dyDescent="0.25">
+    <row r="15" ht="24" customHeight="1" spans="1:70" x14ac:dyDescent="0.25">
       <c r="A15" s="13">
         <v>14</v>
       </c>
@@ -3913,50 +5245,55 @@
         <v>70</v>
       </c>
       <c r="C15" s="14" t="s">
-        <v>124</v>
+        <v>314</v>
       </c>
       <c r="D15" s="14" t="s">
         <v>70</v>
       </c>
       <c r="E15" s="14" t="s">
-        <v>70</v>
+        <v>315</v>
+      </c>
+      <c r="F15" s="14" t="s">
+        <v>316</v>
       </c>
       <c r="G15" s="14" t="s">
-        <v>72</v>
+        <v>317</v>
       </c>
       <c r="H15" s="14" t="s">
-        <v>125</v>
+        <v>318</v>
       </c>
       <c r="I15" s="14" t="s">
-        <v>70</v>
+        <v>319</v>
       </c>
       <c r="J15" s="14" t="s">
-        <v>126</v>
+        <v>320</v>
       </c>
       <c r="K15" s="14" t="s">
-        <v>127</v>
+        <v>321</v>
       </c>
       <c r="L15" s="14" t="s">
-        <v>124</v>
-      </c>
-      <c r="M15" s="1"/>
+        <v>314</v>
+      </c>
+      <c r="M15" s="14" t="s">
+        <v>81</v>
+      </c>
       <c r="N15" s="14" t="s">
-        <v>70</v>
-      </c>
-      <c r="O15" s="15" t="s">
-        <v>70</v>
-      </c>
-      <c r="P15" s="15" t="s">
-        <v>70</v>
-      </c>
-      <c r="Q15" s="16" t="s">
-        <v>70</v>
+        <v>82</v>
+      </c>
+      <c r="O15" s="15">
+        <v>3147240</v>
+      </c>
+      <c r="P15" s="15">
+        <v>-36089</v>
+      </c>
+      <c r="Q15" s="16">
+        <v>-0.01</v>
       </c>
       <c r="R15" s="17" t="s">
-        <v>70</v>
+        <v>83</v>
       </c>
       <c r="S15" s="18" t="s">
-        <v>70</v>
+        <v>322</v>
       </c>
       <c r="T15" s="15" t="s">
         <v>70</v>
@@ -3973,22 +5310,41 @@
       <c r="X15" s="15" t="s">
         <v>70</v>
       </c>
-      <c r="Z15" s="4"/>
+      <c r="Y15" s="19">
+        <v>1</v>
+      </c>
+      <c r="Z15" s="20">
+        <v>266.71</v>
+      </c>
+      <c r="AA15" s="4"/>
+      <c r="AB15" s="1"/>
+      <c r="AC15" s="2"/>
       <c r="AD15" s="19">
         <v>3</v>
       </c>
-      <c r="AF15" s="20">
+      <c r="AE15" s="15">
+        <v>0</v>
+      </c>
+      <c r="AF15" s="21">
         <v>4.6</v>
       </c>
-      <c r="AG15" s="21">
+      <c r="AG15" s="22">
         <v>0</v>
       </c>
+      <c r="AH15" s="20">
+        <v>8.41</v>
+      </c>
       <c r="AI15" s="16">
-        <v>0</v>
-      </c>
-      <c r="AK15" s="1"/>
-      <c r="AL15" s="19" t="s">
-        <v>70</v>
+        <v>0.82</v>
+      </c>
+      <c r="AK15" s="13" t="s">
+        <v>323</v>
+      </c>
+      <c r="AL15" s="19">
+        <v>133</v>
+      </c>
+      <c r="AM15" s="13" t="s">
+        <v>87</v>
       </c>
       <c r="AN15" s="13" t="s">
         <v>70</v>
@@ -3996,17 +5352,27 @@
       <c r="AO15" s="13" t="s">
         <v>70</v>
       </c>
-      <c r="AQ15" s="19" t="s">
-        <v>70</v>
+      <c r="AP15" s="4"/>
+      <c r="AQ15" s="19">
+        <v>8</v>
+      </c>
+      <c r="AR15" s="19">
+        <v>1</v>
+      </c>
+      <c r="AS15" s="14" t="s">
+        <v>324</v>
+      </c>
+      <c r="AT15" s="13" t="s">
+        <v>87</v>
       </c>
       <c r="AU15" s="13" t="s">
-        <v>70</v>
+        <v>325</v>
       </c>
       <c r="AV15" s="14" t="s">
-        <v>70</v>
+        <v>326</v>
       </c>
       <c r="AW15" s="13" t="s">
-        <v>70</v>
+        <v>327</v>
       </c>
       <c r="AX15" s="13" t="s">
         <v>70</v>
@@ -4041,20 +5407,35 @@
       <c r="BH15" s="14" t="s">
         <v>70</v>
       </c>
-      <c r="BK15" s="22" t="s">
-        <v>70</v>
-      </c>
-      <c r="BM15" s="22" t="s">
-        <v>70</v>
-      </c>
-      <c r="BO15" s="22" t="s">
-        <v>70</v>
-      </c>
-      <c r="BQ15" s="22" t="s">
-        <v>70</v>
+      <c r="BJ15" s="23" t="s">
+        <v>328</v>
+      </c>
+      <c r="BK15" s="23" t="s">
+        <v>329</v>
+      </c>
+      <c r="BL15" s="23" t="s">
+        <v>330</v>
+      </c>
+      <c r="BM15" s="23" t="s">
+        <v>331</v>
+      </c>
+      <c r="BN15" s="23" t="s">
+        <v>332</v>
+      </c>
+      <c r="BO15" s="23" t="s">
+        <v>329</v>
+      </c>
+      <c r="BP15" s="23" t="s">
+        <v>333</v>
+      </c>
+      <c r="BQ15" s="23" t="s">
+        <v>334</v>
+      </c>
+      <c r="BR15" s="13" t="s">
+        <v>97</v>
       </c>
     </row>
-    <row r="16" ht="24" customHeight="1" spans="1:69" x14ac:dyDescent="0.25">
+    <row r="16" ht="24" customHeight="1" spans="1:70" x14ac:dyDescent="0.25">
       <c r="A16" s="13">
         <v>15</v>
       </c>
@@ -4062,50 +5443,52 @@
         <v>70</v>
       </c>
       <c r="C16" s="14" t="s">
-        <v>128</v>
+        <v>335</v>
       </c>
       <c r="D16" s="14" t="s">
         <v>70</v>
       </c>
       <c r="E16" s="14" t="s">
-        <v>70</v>
+        <v>336</v>
+      </c>
+      <c r="F16" s="14" t="s">
+        <v>337</v>
       </c>
       <c r="G16" s="14" t="s">
-        <v>72</v>
+        <v>338</v>
       </c>
       <c r="H16" s="14" t="s">
-        <v>129</v>
+        <v>339</v>
       </c>
       <c r="I16" s="14" t="s">
-        <v>70</v>
+        <v>340</v>
       </c>
       <c r="J16" s="14" t="s">
-        <v>130</v>
+        <v>341</v>
       </c>
       <c r="K16" s="14" t="s">
-        <v>131</v>
+        <v>342</v>
       </c>
       <c r="L16" s="14" t="s">
-        <v>128</v>
-      </c>
-      <c r="M16" s="1"/>
+        <v>335</v>
+      </c>
+      <c r="M16" s="14" t="s">
+        <v>81</v>
+      </c>
       <c r="N16" s="14" t="s">
-        <v>70</v>
-      </c>
-      <c r="O16" s="15" t="s">
-        <v>70</v>
-      </c>
-      <c r="P16" s="15" t="s">
-        <v>70</v>
-      </c>
-      <c r="Q16" s="16" t="s">
-        <v>70</v>
+        <v>82</v>
+      </c>
+      <c r="O16" s="15">
+        <v>3841102</v>
+      </c>
+      <c r="Q16" s="16">
+        <v>0</v>
       </c>
       <c r="R16" s="17" t="s">
-        <v>70</v>
+        <v>83</v>
       </c>
       <c r="S16" s="18" t="s">
-        <v>70</v>
+        <v>343</v>
       </c>
       <c r="T16" s="15" t="s">
         <v>70</v>
@@ -4122,10 +5505,16 @@
       <c r="X16" s="15" t="s">
         <v>70</v>
       </c>
+      <c r="Y16" s="19">
+        <v>1</v>
+      </c>
       <c r="Z16" s="4"/>
+      <c r="AA16" s="4"/>
+      <c r="AB16" s="1"/>
+      <c r="AC16" s="2"/>
       <c r="AD16" s="2"/>
       <c r="AF16" s="5"/>
-      <c r="AG16" s="21">
+      <c r="AG16" s="22">
         <v>0</v>
       </c>
       <c r="AI16" s="16">
@@ -4135,15 +5524,24 @@
       <c r="AL16" s="19" t="s">
         <v>70</v>
       </c>
+      <c r="AM16" s="13" t="s">
+        <v>87</v>
+      </c>
       <c r="AN16" s="13" t="s">
         <v>70</v>
       </c>
       <c r="AO16" s="13" t="s">
         <v>70</v>
       </c>
+      <c r="AP16" s="4"/>
       <c r="AQ16" s="19" t="s">
         <v>70</v>
       </c>
+      <c r="AR16" s="2"/>
+      <c r="AS16" s="1"/>
+      <c r="AT16" s="13" t="s">
+        <v>87</v>
+      </c>
       <c r="AU16" s="13" t="s">
         <v>70</v>
       </c>
@@ -4186,23 +5584,30 @@
       <c r="BH16" s="14" t="s">
         <v>70</v>
       </c>
-      <c r="BK16" s="22" t="s">
-        <v>70</v>
-      </c>
-      <c r="BM16" s="22" t="s">
-        <v>70</v>
-      </c>
-      <c r="BO16" s="22" t="s">
-        <v>70</v>
-      </c>
-      <c r="BQ16" s="22" t="s">
-        <v>70</v>
-      </c>
+      <c r="BJ16" s="23" t="s">
+        <v>344</v>
+      </c>
+      <c r="BK16" s="23" t="s">
+        <v>345</v>
+      </c>
+      <c r="BL16" s="1"/>
+      <c r="BM16" s="23" t="s">
+        <v>70</v>
+      </c>
+      <c r="BN16" s="1"/>
+      <c r="BO16" s="23" t="s">
+        <v>70</v>
+      </c>
+      <c r="BP16" s="1"/>
+      <c r="BQ16" s="23" t="s">
+        <v>70</v>
+      </c>
+      <c r="BR16" s="1"/>
     </row>
     <row r="17" ht="28" customHeight="1" spans="1:70" x14ac:dyDescent="0.25">
       <c r="A17" s="24"/>
       <c r="B17" s="24" t="s">
-        <v>132</v>
+        <v>346</v>
       </c>
       <c r="C17" s="24"/>
       <c r="D17" s="24"/>
@@ -4276,90 +5681,125 @@
   </sheetData>
   <hyperlinks>
     <hyperlink ref="C2" r:id="rId1" tooltip="https://www.amazon.de/dp/B0GJSLTZK3"/>
-    <hyperlink ref="G2" r:id="rId2" tooltip="https://www.amazon.deundefined"/>
+    <hyperlink ref="G2" r:id="rId2" tooltip="https://www.amazon.denull"/>
     <hyperlink ref="J2" r:id="rId3" tooltip="https://www.amazon.de/dp/B0GJSLTZK3?psc=1"/>
-    <hyperlink ref="K2" r:id="rId4" tooltip="https://images-eu.ssl-images-amazon.com/images/I/61AVz1Oy8NL._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L2" r:id="rId5" tooltip="https://www.amazon.de/dp/B0GJSLTZK3"/>
-    <hyperlink ref="C3" r:id="rId6" tooltip="https://www.amazon.de/dp/B0FJGW9H14"/>
-    <hyperlink ref="G3" r:id="rId7" tooltip="https://www.amazon.deundefined"/>
-    <hyperlink ref="J3" r:id="rId8" tooltip="https://www.amazon.de/dp/B0FJGW9H14?psc=1"/>
-    <hyperlink ref="K3" r:id="rId9" tooltip="https://images-eu.ssl-images-amazon.com/images/I/61ACeClalUL._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L3" r:id="rId10" tooltip="https://www.amazon.de/dp/B0FJGW9H14"/>
-    <hyperlink ref="C4" r:id="rId11" tooltip="https://www.amazon.de/dp/B0DJ7MYQ7X"/>
-    <hyperlink ref="G4" r:id="rId12" tooltip="https://www.amazon.deundefined"/>
-    <hyperlink ref="J4" r:id="rId13" tooltip="https://www.amazon.de/dp/B0DJ7MYQ7X?psc=1"/>
-    <hyperlink ref="K4" r:id="rId14" tooltip="https://images-eu.ssl-images-amazon.com/images/I/51li4JItSNL._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L4" r:id="rId15" tooltip="https://www.amazon.de/dp/B0DJ7MYQ7X"/>
-    <hyperlink ref="C5" r:id="rId16" tooltip="https://www.amazon.de/dp/B0DPP6C5YP"/>
-    <hyperlink ref="G5" r:id="rId17" tooltip="https://www.amazon.deundefined"/>
-    <hyperlink ref="J5" r:id="rId18" tooltip="https://www.amazon.de/dp/B0DPP6C5YP?psc=1"/>
-    <hyperlink ref="K5" r:id="rId19" tooltip="https://images-eu.ssl-images-amazon.com/images/I/61HEpMCMG9L._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L5" r:id="rId20" tooltip="https://www.amazon.de/dp/B0DPP6C5YP"/>
-    <hyperlink ref="C6" r:id="rId21" tooltip="https://www.amazon.de/dp/B0FX2MMRK3"/>
-    <hyperlink ref="G6" r:id="rId22" tooltip="https://www.amazon.deundefined"/>
-    <hyperlink ref="J6" r:id="rId23" tooltip="https://www.amazon.de/dp/B0FX2MMRK3?psc=1"/>
-    <hyperlink ref="K6" r:id="rId24" tooltip="https://images-eu.ssl-images-amazon.com/images/I/71qYMu5c95L._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L6" r:id="rId25" tooltip="https://www.amazon.de/dp/B0FX2MMRK3"/>
-    <hyperlink ref="C7" r:id="rId26" tooltip="https://www.amazon.de/dp/B0H62W3T31"/>
-    <hyperlink ref="G7" r:id="rId27" tooltip="https://www.amazon.deundefined"/>
-    <hyperlink ref="J7" r:id="rId28" tooltip="https://www.amazon.de/dp/B0H62W3T31?psc=1"/>
-    <hyperlink ref="K7" r:id="rId29" tooltip="https://images-eu.ssl-images-amazon.com/images/I/81UYR2XHqKL._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L7" r:id="rId30" tooltip="https://www.amazon.de/dp/B0H62W3T31"/>
-    <hyperlink ref="C8" r:id="rId31" tooltip="https://www.amazon.de/dp/B0FN46V7CN"/>
-    <hyperlink ref="G8" r:id="rId32" tooltip="https://www.amazon.deundefined"/>
-    <hyperlink ref="J8" r:id="rId33" tooltip="https://www.amazon.de/dp/B0FN46V7CN?psc=1"/>
-    <hyperlink ref="K8" r:id="rId34" tooltip="https://images-eu.ssl-images-amazon.com/images/I/61pE-Rb8EaL._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L8" r:id="rId35" tooltip="https://www.amazon.de/dp/B0FN46V7CN"/>
-    <hyperlink ref="C9" r:id="rId36" tooltip="https://www.amazon.de/dp/B0FR44ZBJP"/>
-    <hyperlink ref="G9" r:id="rId37" tooltip="https://www.amazon.deundefined"/>
-    <hyperlink ref="J9" r:id="rId38" tooltip="https://www.amazon.de/dp/B0FR44ZBJP?psc=1"/>
-    <hyperlink ref="K9" r:id="rId39" tooltip="https://images-eu.ssl-images-amazon.com/images/I/61YVBi7d7CL._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L9" r:id="rId40" tooltip="https://www.amazon.de/dp/B0FR44ZBJP"/>
-    <hyperlink ref="C10" r:id="rId41" tooltip="https://www.amazon.de/dp/B0G66NWWCR"/>
-    <hyperlink ref="G10" r:id="rId42" tooltip="https://www.amazon.deundefined"/>
-    <hyperlink ref="J10" r:id="rId43" tooltip="https://www.amazon.de/dp/B0G66NWWCR?psc=1"/>
-    <hyperlink ref="K10" r:id="rId44" tooltip="https://images-eu.ssl-images-amazon.com/images/I/61xEbwRg-HL._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L10" r:id="rId45" tooltip="https://www.amazon.de/dp/B0G66NWWCR"/>
-    <hyperlink ref="C11" r:id="rId46" tooltip="https://www.amazon.de/dp/B0DGV9F4X3"/>
-    <hyperlink ref="G11" r:id="rId47" tooltip="https://www.amazon.deundefined"/>
-    <hyperlink ref="J11" r:id="rId48" tooltip="https://www.amazon.de/dp/B0DGV9F4X3?psc=1"/>
-    <hyperlink ref="K11" r:id="rId49" tooltip="https://images-eu.ssl-images-amazon.com/images/I/61w5mQfWH9L._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L11" r:id="rId50" tooltip="https://www.amazon.de/dp/B0DGV9F4X3"/>
-    <hyperlink ref="C12" r:id="rId51" tooltip="https://www.amazon.de/dp/B0GL7P6391"/>
-    <hyperlink ref="G12" r:id="rId52" tooltip="https://www.amazon.deundefined"/>
-    <hyperlink ref="J12" r:id="rId53" tooltip="https://www.amazon.de/dp/B0GL7P6391?psc=1"/>
-    <hyperlink ref="K12" r:id="rId54" tooltip="https://images-eu.ssl-images-amazon.com/images/I/61KFErwK5aL._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L12" r:id="rId55" tooltip="https://www.amazon.de/dp/B0GL7P6391"/>
-    <hyperlink ref="C13" r:id="rId56" tooltip="https://www.amazon.de/dp/B0H8Y83NN7"/>
-    <hyperlink ref="G13" r:id="rId57" tooltip="https://www.amazon.deundefined"/>
-    <hyperlink ref="J13" r:id="rId58" tooltip="https://www.amazon.de/dp/B0H8Y83NN7?psc=1"/>
-    <hyperlink ref="K13" r:id="rId59" tooltip="https://images-eu.ssl-images-amazon.com/images/I/71Rk7RmZfuL._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L13" r:id="rId60" tooltip="https://www.amazon.de/dp/B0H8Y83NN7"/>
-    <hyperlink ref="C14" r:id="rId61" tooltip="https://www.amazon.de/dp/B0FPMB88DH"/>
-    <hyperlink ref="G14" r:id="rId62" tooltip="https://www.amazon.deundefined"/>
-    <hyperlink ref="J14" r:id="rId63" tooltip="https://www.amazon.de/dp/B0FPMB88DH?psc=1"/>
-    <hyperlink ref="K14" r:id="rId64" tooltip="https://images-eu.ssl-images-amazon.com/images/I/71Veas8E33L._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L14" r:id="rId65" tooltip="https://www.amazon.de/dp/B0FPMB88DH"/>
-    <hyperlink ref="C15" r:id="rId66" tooltip="https://www.amazon.de/dp/B0GX7CQRDX"/>
-    <hyperlink ref="G15" r:id="rId67" tooltip="https://www.amazon.deundefined"/>
-    <hyperlink ref="J15" r:id="rId68" tooltip="https://www.amazon.de/dp/B0GX7CQRDX?psc=1"/>
-    <hyperlink ref="K15" r:id="rId69" tooltip="https://images-eu.ssl-images-amazon.com/images/I/611qVIQFvkL._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L15" r:id="rId70" tooltip="https://www.amazon.de/dp/B0GX7CQRDX"/>
-    <hyperlink ref="C16" r:id="rId71" tooltip="https://www.amazon.de/dp/B0BJ7SZ1W1"/>
-    <hyperlink ref="G16" r:id="rId72" tooltip="https://www.amazon.deundefined"/>
-    <hyperlink ref="J16" r:id="rId73" tooltip="https://www.amazon.de/dp/B0BJ7SZ1W1?psc=1"/>
-    <hyperlink ref="K16" r:id="rId74" tooltip="https://images-eu.ssl-images-amazon.com/images/I/51ZkjjdFteL._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L16" r:id="rId75" tooltip="https://www.amazon.de/dp/B0BJ7SZ1W1"/>
+    <hyperlink ref="K2" r:id="rId4" tooltip="https://images-na.ssl-images-amazon.com/images/I/61AVz1Oy8NL._AC_US600_.jpg"/>
+    <hyperlink ref="L2" r:id="rId5" tooltip="https://www.amazon.de/dp/B0H8LGC3LM"/>
+    <hyperlink ref="M2" r:id="rId6" tooltip="https://www.amazon.de/b?node=218877962031"/>
+    <hyperlink ref="N2" r:id="rId7"/>
+    <hyperlink ref="C3" r:id="rId8" tooltip="https://www.amazon.de/dp/B0FJGW9H14"/>
+    <hyperlink ref="G3" r:id="rId9" tooltip="https://www.amazon.de/stores/Rowenta/page/F8BD1336-17F4-4FC9-B31C-02321E3AC422?lp_asin=B0FJGW9H14&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto"/>
+    <hyperlink ref="J3" r:id="rId10" tooltip="https://www.amazon.de/dp/B0FJGW9H14?psc=1"/>
+    <hyperlink ref="K3" r:id="rId11" tooltip="https://images-na.ssl-images-amazon.com/images/I/61ACeClalUL._AC_US600_.jpg"/>
+    <hyperlink ref="L3" r:id="rId12" tooltip="https://www.amazon.de/dp/B0HJRYCGD6"/>
+    <hyperlink ref="M3" r:id="rId13" tooltip="https://www.amazon.de/b?node=218877962031"/>
+    <hyperlink ref="N3" r:id="rId14"/>
+    <hyperlink ref="C4" r:id="rId15" tooltip="https://www.amazon.de/dp/B0DJ7MYQ7X"/>
+    <hyperlink ref="G4" r:id="rId16" tooltip="https://www.amazon.de/stores/roborock/page/68FE67F4-6CEB-4B2C-AE25-2300177358D6?lp_asin=B0DJ7MYQ7X&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto"/>
+    <hyperlink ref="J4" r:id="rId17" tooltip="https://www.amazon.de/dp/B0DJ7MYQ7X?psc=1"/>
+    <hyperlink ref="K4" r:id="rId18" tooltip="https://images-na.ssl-images-amazon.com/images/I/51li4JItSNL._AC_US600_.jpg"/>
+    <hyperlink ref="L4" r:id="rId19" tooltip="https://www.amazon.de/dp/B0HKMTL7TP"/>
+    <hyperlink ref="M4" r:id="rId20" tooltip="https://www.amazon.de/b?node=218877962031"/>
+    <hyperlink ref="N4" r:id="rId21"/>
+    <hyperlink ref="C5" r:id="rId22" tooltip="https://www.amazon.de/dp/B0DPP6C5YP"/>
+    <hyperlink ref="G5" r:id="rId23" tooltip="https://www.amazon.de/stores/Tineco/page/7C365934-3A47-4B27-95CB-A4F47FAA26F6?lp_asin=B0DPP6C5YP&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto"/>
+    <hyperlink ref="J5" r:id="rId24" tooltip="https://www.amazon.de/dp/B0DPP6C5YP?psc=1"/>
+    <hyperlink ref="K5" r:id="rId25" tooltip="https://m.media-amazon.com/images/I/31d14GorfwL._AC_US600_.jpg"/>
+    <hyperlink ref="L5" r:id="rId26" tooltip="https://www.amazon.de/dp/B0HFPXNLLM"/>
+    <hyperlink ref="M5" r:id="rId27" tooltip="https://www.amazon.de/b?node=218877962031"/>
+    <hyperlink ref="N5" r:id="rId28"/>
+    <hyperlink ref="AW5" r:id="rId29" tooltip="https://www.amazon.de/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A2QOI9TFEBV4J3"/>
+    <hyperlink ref="C6" r:id="rId30" tooltip="https://www.amazon.de/dp/B0FX2MMRK3"/>
+    <hyperlink ref="G6" r:id="rId31" tooltip="https://www.amazon.de/stores/Tineco/page/7C365934-3A47-4B27-95CB-A4F47FAA26F6?lp_asin=B0FX2MMRK3&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto"/>
+    <hyperlink ref="J6" r:id="rId32" tooltip="https://www.amazon.de/dp/B0FX2MMRK3?psc=1"/>
+    <hyperlink ref="K6" r:id="rId33" tooltip="https://images-na.ssl-images-amazon.com/images/I/71qYMu5c95L._AC_US600_.jpg"/>
+    <hyperlink ref="L6" r:id="rId34" tooltip="https://www.amazon.de/dp/B0HFN25V8Q"/>
+    <hyperlink ref="M6" r:id="rId35" tooltip="https://www.amazon.de/b?node=218877962031"/>
+    <hyperlink ref="N6" r:id="rId36"/>
+    <hyperlink ref="AW6" r:id="rId37" tooltip="https://www.amazon.de/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A2QOI9TFEBV4J3"/>
+    <hyperlink ref="C7" r:id="rId38" tooltip="https://www.amazon.de/dp/B0H62W3T31"/>
+    <hyperlink ref="G7" r:id="rId39" tooltip="https://www.amazon.de/s/ref=bl_dp_s_web_0?ie=UTF8&amp;search-type=ss&amp;index=kitchen-de&amp;field-keywords=ATEC+Clean"/>
+    <hyperlink ref="J7" r:id="rId40" tooltip="https://www.amazon.de/dp/B0H62W3T31?psc=1"/>
+    <hyperlink ref="K7" r:id="rId41" tooltip="https://m.media-amazon.com/images/I/41Z9+MKiOKL._AC_US200_.jpg"/>
+    <hyperlink ref="L7" r:id="rId42" tooltip="https://www.amazon.de/dp/B0H62W3T31"/>
+    <hyperlink ref="M7" r:id="rId43" tooltip="https://www.amazon.de/b?node=218877962031"/>
+    <hyperlink ref="N7" r:id="rId44"/>
+    <hyperlink ref="C8" r:id="rId45" tooltip="https://www.amazon.de/dp/B0FN46V7CN"/>
+    <hyperlink ref="G8" r:id="rId46" tooltip="https://www.amazon.de/stores/Eureka/page/4ABB8AC3-B138-4CAB-9371-548936230037?lp_asin=B0FN46V7CN&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto&amp;bl_grd_status=override"/>
+    <hyperlink ref="J8" r:id="rId47" tooltip="https://www.amazon.de/dp/B0FN46V7CN?psc=1"/>
+    <hyperlink ref="K8" r:id="rId48" tooltip="https://images-na.ssl-images-amazon.com/images/I/61pE-Rb8EaL._AC_US600_.jpg"/>
+    <hyperlink ref="L8" r:id="rId49" tooltip="https://www.amazon.de/dp/B0FN46V7CN"/>
+    <hyperlink ref="M8" r:id="rId50" tooltip="https://www.amazon.de/b?node=218877962031"/>
+    <hyperlink ref="N8" r:id="rId51"/>
+    <hyperlink ref="C9" r:id="rId52" tooltip="https://www.amazon.de/dp/B0FR44ZBJP"/>
+    <hyperlink ref="G9" r:id="rId53" tooltip="https://www.amazon.de/stores/Rowenta/page/F8BD1336-17F4-4FC9-B31C-02321E3AC422?lp_asin=B0FR44ZBJP&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto"/>
+    <hyperlink ref="J9" r:id="rId54" tooltip="https://www.amazon.de/dp/B0FR44ZBJP?psc=1"/>
+    <hyperlink ref="K9" r:id="rId55" tooltip="https://m.media-amazon.com/images/I/31da21x3JcL._AC_US600_.jpg"/>
+    <hyperlink ref="L9" r:id="rId56" tooltip="https://www.amazon.de/dp/B0GPR921Z1"/>
+    <hyperlink ref="M9" r:id="rId57" tooltip="https://www.amazon.de/b?node=218877962031"/>
+    <hyperlink ref="N9" r:id="rId58"/>
+    <hyperlink ref="C10" r:id="rId59" tooltip="https://www.amazon.de/dp/B0DGV9F4X3"/>
+    <hyperlink ref="G10" r:id="rId60" tooltip="https://www.amazon.de/stores/Rowenta/page/F8BD1336-17F4-4FC9-B31C-02321E3AC422?lp_asin=B0DGV9F4X3&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto"/>
+    <hyperlink ref="J10" r:id="rId61" tooltip="https://www.amazon.de/dp/B0DGV9F4X3?psc=1"/>
+    <hyperlink ref="K10" r:id="rId62" tooltip="https://m.media-amazon.com/images/I/31S3KICrUsL._AC_US600_.jpg"/>
+    <hyperlink ref="L10" r:id="rId63" tooltip="https://www.amazon.de/dp/B0H7XLDTB1"/>
+    <hyperlink ref="M10" r:id="rId64" tooltip="https://www.amazon.de/b?node=218877962031"/>
+    <hyperlink ref="N10" r:id="rId65"/>
+    <hyperlink ref="C11" r:id="rId66" tooltip="https://www.amazon.de/dp/B0G66NWWCR"/>
+    <hyperlink ref="G11" r:id="rId67" tooltip="https://www.amazon.de/stores/BoschDIY/page/17690673-38F2-4715-A4D6-6D23BC5AC7E6?lp_asin=B0G66NWWCR&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto"/>
+    <hyperlink ref="J11" r:id="rId68" tooltip="https://www.amazon.de/dp/B0G66NWWCR?psc=1"/>
+    <hyperlink ref="K11" r:id="rId69" tooltip="https://m.media-amazon.com/images/W/BW_MEDIAX_AVIF_MEASUREMENT_1306696-T4/images/I/31ZFL7asYeL._AC_US600_.jpg"/>
+    <hyperlink ref="L11" r:id="rId70" tooltip="https://www.amazon.de/dp/B0H6MY3KH1"/>
+    <hyperlink ref="M11" r:id="rId71" tooltip="https://www.amazon.de/b?node=218877962031"/>
+    <hyperlink ref="N11" r:id="rId72"/>
+    <hyperlink ref="C12" r:id="rId73" tooltip="https://www.amazon.de/dp/B0GL7P6391"/>
+    <hyperlink ref="G12" r:id="rId74" tooltip="https://www.amazon.de/stores/JONR/page/DAC39F39-859B-4414-BC57-D789ECE2CA82?lp_asin=B0GL7P6391&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto&amp;bl_grd_status=override"/>
+    <hyperlink ref="J12" r:id="rId75" tooltip="https://www.amazon.de/dp/B0GL7P6391?psc=1"/>
+    <hyperlink ref="K12" r:id="rId76" tooltip="https://images-na.ssl-images-amazon.com/images/I/61KFErwK5aL._AC_US600_.jpg"/>
+    <hyperlink ref="L12" r:id="rId77" tooltip="https://www.amazon.de/dp/B0GL7P6391"/>
+    <hyperlink ref="M12" r:id="rId78" tooltip="https://www.amazon.de/b?node=218877962031"/>
+    <hyperlink ref="N12" r:id="rId79"/>
+    <hyperlink ref="AW12" r:id="rId80" tooltip="https://www.amazon.de/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A17T2O4U8TIBEZ"/>
+    <hyperlink ref="C13" r:id="rId81" tooltip="https://www.amazon.de/dp/B0FPMB88DH"/>
+    <hyperlink ref="G13" r:id="rId82" tooltip="https://www.amazon.de/stores/Eureka/page/4ABB8AC3-B138-4CAB-9371-548936230037?lp_asin=B0FPMB88DH&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto&amp;bl_grd_status=override"/>
+    <hyperlink ref="J13" r:id="rId83" tooltip="https://www.amazon.de/dp/B0FPMB88DH?psc=1"/>
+    <hyperlink ref="K13" r:id="rId84" tooltip="https://images-na.ssl-images-amazon.com/images/I/71Veas8E33L._AC_US600_.jpg"/>
+    <hyperlink ref="L13" r:id="rId85" tooltip="https://www.amazon.de/dp/B0FPMB88DH"/>
+    <hyperlink ref="M13" r:id="rId86" tooltip="https://www.amazon.de/b?node=218877962031"/>
+    <hyperlink ref="N13" r:id="rId87"/>
+    <hyperlink ref="C14" r:id="rId88" tooltip="https://www.amazon.de/dp/B0H8Y83NN7"/>
+    <hyperlink ref="G14" r:id="rId89" tooltip="https://www.amazon.de/s/ref=bl_dp_s_web_0?ie=UTF8&amp;search-type=ss&amp;index=kitchen-de&amp;field-keywords=UtaUla"/>
+    <hyperlink ref="J14" r:id="rId90" tooltip="https://www.amazon.de/dp/B0H8Y83NN7?psc=1"/>
+    <hyperlink ref="K14" r:id="rId91" tooltip="https://images-na.ssl-images-amazon.com/images/I/71Rk7RmZfuL._AC_US600_.jpg"/>
+    <hyperlink ref="L14" r:id="rId92" tooltip="https://www.amazon.de/dp/B0H8Y83NN7"/>
+    <hyperlink ref="M14" r:id="rId93" tooltip="https://www.amazon.de/b?node=218877962031"/>
+    <hyperlink ref="N14" r:id="rId94"/>
+    <hyperlink ref="AW14" r:id="rId95" tooltip="https://www.amazon.de/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A2TW0HFVR94W5Z"/>
+    <hyperlink ref="C15" r:id="rId96" tooltip="https://www.amazon.de/dp/B0GX7CQRDX"/>
+    <hyperlink ref="G15" r:id="rId97" tooltip="https://www.amazon.de/stores/MOVA/page/C421873F-2042-459A-B673-3BA824983D27?lp_asin=B0GX7CQRDX&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto&amp;bl_grd_status=override"/>
+    <hyperlink ref="J15" r:id="rId98" tooltip="https://www.amazon.de/dp/B0GX7CQRDX?psc=1"/>
+    <hyperlink ref="K15" r:id="rId99" tooltip="https://images-na.ssl-images-amazon.com/images/I/611qVIQFvkL._AC_US600_.jpg"/>
+    <hyperlink ref="L15" r:id="rId100" tooltip="https://www.amazon.de/dp/B0GX7CQRDX"/>
+    <hyperlink ref="M15" r:id="rId101" tooltip="https://www.amazon.de/b?node=218877962031"/>
+    <hyperlink ref="N15" r:id="rId102"/>
+    <hyperlink ref="AW15" r:id="rId103" tooltip="https://www.amazon.de/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A3TSTGWB8M3T3Z"/>
+    <hyperlink ref="C16" r:id="rId104" tooltip="https://www.amazon.de/dp/B0BJ7SZ1W1"/>
+    <hyperlink ref="G16" r:id="rId105" tooltip="https://www.amazon.de/stores/K%C3%A4rcher/page/EFE3653A-1163-432C-A85B-0486A31C0E3D?lp_asin=B0BJ7SZ1W1&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto"/>
+    <hyperlink ref="J16" r:id="rId106" tooltip="https://www.amazon.de/dp/B0BJ7SZ1W1?psc=1"/>
+    <hyperlink ref="K16" r:id="rId107" tooltip="https://m.media-amazon.com/images/I/31m5B2TrvrL._AC_US200_.jpg"/>
+    <hyperlink ref="L16" r:id="rId108" tooltip="https://www.amazon.de/dp/B0BJ7SZ1W1"/>
+    <hyperlink ref="M16" r:id="rId109" tooltip="https://www.amazon.de/b?node=218877962031"/>
+    <hyperlink ref="N16" r:id="rId110"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
-  <drawing r:id="rId76"/>
+  <drawing r:id="rId111"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G2"/>
+  <dimension ref="A1:G11"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="25" style="1" customWidth="1"/>
@@ -4379,38 +5819,245 @@
         <v>21</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>133</v>
+        <v>347</v>
       </c>
       <c r="E1" s="8" t="s">
-        <v>134</v>
+        <v>348</v>
       </c>
       <c r="F1" s="10" t="s">
-        <v>135</v>
+        <v>349</v>
       </c>
       <c r="G1" s="12" t="s">
-        <v>136</v>
+        <v>350</v>
       </c>
     </row>
     <row r="2" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="14" t="s">
-        <v>137</v>
+        <v>74</v>
       </c>
       <c r="B2" s="15">
+        <v>7771</v>
+      </c>
+      <c r="C2" s="15">
+        <v>1552374</v>
+      </c>
+      <c r="D2" s="15">
+        <v>53292</v>
+      </c>
+      <c r="E2" s="15">
+        <v>10645876</v>
+      </c>
+      <c r="F2" s="20">
+        <v>199.77</v>
+      </c>
+      <c r="G2" s="22">
+        <v>0.7809999999999999</v>
+      </c>
+    </row>
+    <row r="3" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A3" s="14" t="s">
+        <v>101</v>
+      </c>
+      <c r="B3" s="15">
+        <v>1514</v>
+      </c>
+      <c r="C3" s="15">
+        <v>399398</v>
+      </c>
+      <c r="D3" s="15">
+        <v>21365</v>
+      </c>
+      <c r="E3" s="15">
+        <v>5636158</v>
+      </c>
+      <c r="F3" s="20">
+        <v>263.8</v>
+      </c>
+      <c r="G3" s="22">
+        <v>0.1522</v>
+      </c>
+    </row>
+    <row r="4" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A4" s="14" t="s">
+        <v>140</v>
+      </c>
+      <c r="B4" s="15">
+        <v>374</v>
+      </c>
+      <c r="C4" s="15">
+        <v>233376</v>
+      </c>
+      <c r="D4" s="15">
+        <v>17171</v>
+      </c>
+      <c r="E4" s="15">
+        <v>10714704</v>
+      </c>
+      <c r="F4" s="20">
+        <v>624</v>
+      </c>
+      <c r="G4" s="22">
+        <v>0.037599999999999995</v>
+      </c>
+    </row>
+    <row r="5" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A5" s="14" t="s">
+        <v>245</v>
+      </c>
+      <c r="B5" s="15">
+        <v>269</v>
+      </c>
+      <c r="C5" s="15">
+        <v>19059</v>
+      </c>
+      <c r="D5" s="15">
+        <v>991</v>
+      </c>
+      <c r="E5" s="15">
+        <v>70212</v>
+      </c>
+      <c r="F5" s="20">
+        <v>70.85</v>
+      </c>
+      <c r="G5" s="22">
+        <v>0.027000000000000003</v>
+      </c>
+    </row>
+    <row r="6" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A6" s="14" t="s">
+        <v>192</v>
+      </c>
+      <c r="B6" s="15">
+        <v>14</v>
+      </c>
+      <c r="C6" s="15">
+        <v>4153</v>
+      </c>
+      <c r="D6" s="15">
+        <v>2513</v>
+      </c>
+      <c r="E6" s="15">
+        <v>745406</v>
+      </c>
+      <c r="F6" s="20">
+        <v>296.62</v>
+      </c>
+      <c r="G6" s="22">
+        <v>0.0014000000000000002</v>
+      </c>
+    </row>
+    <row r="7" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A7" s="14" t="s">
+        <v>296</v>
+      </c>
+      <c r="B7" s="15">
+        <v>8</v>
+      </c>
+      <c r="C7" s="15">
+        <v>816</v>
+      </c>
+      <c r="D7" s="15">
+        <v>30</v>
+      </c>
+      <c r="E7" s="15">
+        <v>3060</v>
+      </c>
+      <c r="F7" s="20">
+        <v>101.99</v>
+      </c>
+      <c r="G7" s="22">
+        <v>0.0008</v>
+      </c>
+    </row>
+    <row r="8" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A8" s="14" t="s">
+        <v>181</v>
+      </c>
+      <c r="B8" s="15">
         <v>0</v>
       </c>
-      <c r="C2" s="15">
+      <c r="C8" s="15">
         <v>0</v>
       </c>
-      <c r="D2" s="15">
+      <c r="D8" s="15">
         <v>0</v>
       </c>
-      <c r="E2" s="15">
+      <c r="E8" s="15">
         <v>0</v>
       </c>
-      <c r="F2" s="23">
-        <v>87.01</v>
-      </c>
-      <c r="G2" s="21">
+      <c r="F8" s="20">
+        <v>0</v>
+      </c>
+      <c r="G8" s="22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A9" s="14" t="s">
+        <v>260</v>
+      </c>
+      <c r="B9" s="15">
+        <v>0</v>
+      </c>
+      <c r="C9" s="15">
+        <v>0</v>
+      </c>
+      <c r="D9" s="15">
+        <v>356</v>
+      </c>
+      <c r="E9" s="15">
+        <v>113916</v>
+      </c>
+      <c r="F9" s="20">
+        <v>319.99</v>
+      </c>
+      <c r="G9" s="22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A10" s="14" t="s">
+        <v>316</v>
+      </c>
+      <c r="B10" s="15">
+        <v>0</v>
+      </c>
+      <c r="C10" s="15">
+        <v>0</v>
+      </c>
+      <c r="D10" s="15">
+        <v>0</v>
+      </c>
+      <c r="E10" s="15">
+        <v>0</v>
+      </c>
+      <c r="F10" s="20">
+        <v>266.71</v>
+      </c>
+      <c r="G10" s="22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A11" s="14" t="s">
+        <v>337</v>
+      </c>
+      <c r="B11" s="15">
+        <v>0</v>
+      </c>
+      <c r="C11" s="15">
+        <v>0</v>
+      </c>
+      <c r="D11" s="15">
+        <v>0</v>
+      </c>
+      <c r="E11" s="15">
+        <v>0</v>
+      </c>
+      <c r="F11" s="20">
+        <v>0</v>
+      </c>
+      <c r="G11" s="22">
         <v>0</v>
       </c>
     </row>
@@ -4422,7 +6069,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G2"/>
+  <dimension ref="A1:G7"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="25" style="1" customWidth="1"/>
@@ -4433,7 +6080,7 @@
   <sheetData>
     <row r="1" ht="27" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" s="7" t="s">
-        <v>138</v>
+        <v>351</v>
       </c>
       <c r="B1" s="8" t="s">
         <v>19</v>
@@ -4442,38 +6089,153 @@
         <v>21</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>133</v>
+        <v>347</v>
       </c>
       <c r="E1" s="8" t="s">
-        <v>134</v>
+        <v>348</v>
       </c>
       <c r="F1" s="10" t="s">
-        <v>135</v>
+        <v>349</v>
       </c>
       <c r="G1" s="12" t="s">
-        <v>136</v>
+        <v>350</v>
       </c>
     </row>
     <row r="2" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="14" t="s">
-        <v>139</v>
+        <v>88</v>
       </c>
       <c r="B2" s="15">
+        <v>9568</v>
+      </c>
+      <c r="C2" s="15">
+        <v>2218616</v>
+      </c>
+      <c r="D2" s="15">
+        <v>78161</v>
+      </c>
+      <c r="E2" s="15">
+        <v>18123875</v>
+      </c>
+      <c r="F2" s="20">
+        <v>231.88</v>
+      </c>
+      <c r="G2" s="22">
+        <v>0.9616</v>
+      </c>
+    </row>
+    <row r="3" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A3" s="14" t="s">
+        <v>140</v>
+      </c>
+      <c r="B3" s="15">
+        <v>374</v>
+      </c>
+      <c r="C3" s="15">
+        <v>233376</v>
+      </c>
+      <c r="D3" s="15">
+        <v>17171</v>
+      </c>
+      <c r="E3" s="15">
+        <v>10714704</v>
+      </c>
+      <c r="F3" s="20">
+        <v>624</v>
+      </c>
+      <c r="G3" s="22">
+        <v>0.037599999999999995</v>
+      </c>
+    </row>
+    <row r="4" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A4" s="14" t="s">
+        <v>296</v>
+      </c>
+      <c r="B4" s="15">
+        <v>8</v>
+      </c>
+      <c r="C4" s="15">
+        <v>816</v>
+      </c>
+      <c r="D4" s="15">
+        <v>30</v>
+      </c>
+      <c r="E4" s="15">
+        <v>3060</v>
+      </c>
+      <c r="F4" s="20">
+        <v>101.99</v>
+      </c>
+      <c r="G4" s="22">
+        <v>0.0008</v>
+      </c>
+    </row>
+    <row r="5" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A5" s="14" t="s">
+        <v>352</v>
+      </c>
+      <c r="B5" s="15">
         <v>0</v>
       </c>
-      <c r="C2" s="15">
+      <c r="C5" s="15">
         <v>0</v>
       </c>
-      <c r="D2" s="15">
+      <c r="D5" s="15">
         <v>0</v>
       </c>
-      <c r="E2" s="15">
+      <c r="E5" s="15">
         <v>0</v>
       </c>
-      <c r="F2" s="23">
-        <v>87.01</v>
-      </c>
-      <c r="G2" s="21">
+      <c r="F5" s="20">
+        <v>0</v>
+      </c>
+      <c r="G5" s="22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A6" s="14" t="s">
+        <v>268</v>
+      </c>
+      <c r="B6" s="15">
+        <v>0</v>
+      </c>
+      <c r="C6" s="15">
+        <v>0</v>
+      </c>
+      <c r="D6" s="15">
+        <v>356</v>
+      </c>
+      <c r="E6" s="15">
+        <v>113916</v>
+      </c>
+      <c r="F6" s="20">
+        <v>319.99</v>
+      </c>
+      <c r="G6" s="22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A7" s="14" t="s">
+        <v>324</v>
+      </c>
+      <c r="B7" s="15">
+        <v>0</v>
+      </c>
+      <c r="C7" s="15">
+        <v>0</v>
+      </c>
+      <c r="D7" s="15">
+        <v>0</v>
+      </c>
+      <c r="E7" s="15">
+        <v>0</v>
+      </c>
+      <c r="F7" s="20">
+        <v>266.71</v>
+      </c>
+      <c r="G7" s="22">
         <v>0</v>
       </c>
     </row>
@@ -4493,37 +6255,37 @@
   <sheetData>
     <row r="1" ht="45" customHeight="1" spans="1:1" s="31" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="32" t="s">
-        <v>140</v>
+        <v>353</v>
       </c>
     </row>
     <row r="2" ht="45" customHeight="1" spans="1:1" s="31" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="32" t="s">
-        <v>141</v>
+        <v>354</v>
       </c>
     </row>
     <row r="3" ht="200" customHeight="1" spans="1:1" s="31" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="32" t="s">
-        <v>142</v>
+        <v>355</v>
       </c>
     </row>
     <row r="4" ht="45" customHeight="1" spans="1:1" s="31" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="32" t="s">
-        <v>143</v>
+        <v>356</v>
       </c>
     </row>
     <row r="5" ht="45" customHeight="1" spans="1:1" s="31" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="32" t="s">
-        <v>144</v>
+        <v>357</v>
       </c>
     </row>
     <row r="6" ht="45" customHeight="1" spans="1:1" s="33" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="34" t="s">
-        <v>145</v>
+        <v>358</v>
       </c>
     </row>
     <row r="7" ht="45" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7" s="35" t="s">
-        <v>146</v>
+        <v>359</v>
       </c>
     </row>
   </sheetData>
